--- a/artfynd/A 17406-2025 artfynd.xlsx
+++ b/artfynd/A 17406-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ82"/>
+  <dimension ref="A1:AZ93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3336,10 +3336,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124444867</v>
+        <v>136644424</v>
       </c>
       <c r="B27" t="n">
-        <v>96458</v>
+        <v>96554</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3347,41 +3347,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2818</v>
+        <v>2812</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>699944</v>
+        <v>699918</v>
       </c>
       <c r="R27" t="n">
-        <v>6660374</v>
+        <v>6660369</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3405,12 +3401,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3419,34 +3425,33 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124444867</t>
+          <t>https://artportalen.se/Sighting/136644424</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128760316</v>
+        <v>124444867</v>
       </c>
       <c r="B28" t="n">
-        <v>91680</v>
+        <v>96458</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3454,37 +3459,41 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3215</v>
+        <v>2818</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>699935</v>
+        <v>699944</v>
       </c>
       <c r="R28" t="n">
-        <v>6660294</v>
+        <v>6660374</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3508,12 +3517,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3522,55 +3531,56 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Gillis Aronsson</t>
+          <t>Viktor Lund, Martin Axegård</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128760316</t>
+          <t>https://artportalen.se/Sighting/124444867</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128760310</v>
+        <v>128760316</v>
       </c>
       <c r="B29" t="n">
-        <v>91361</v>
+        <v>91680</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3286</v>
+        <v>3215</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3580,10 +3590,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>699951</v>
+        <v>699935</v>
       </c>
       <c r="R29" t="n">
-        <v>6660295</v>
+        <v>6660294</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3641,53 +3651,54 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128760310</t>
+          <t>https://artportalen.se/Sighting/128760316</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>112662551</v>
+        <v>128760310</v>
       </c>
       <c r="B30" t="n">
-        <v>87412</v>
+        <v>91361</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3624</v>
+        <v>3286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
+          <t>Clavariadelphus truncatus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Quél.) Donk</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>699830</v>
+        <v>699951</v>
       </c>
       <c r="R30" t="n">
-        <v>6660298</v>
+        <v>6660295</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3711,12 +3722,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3725,38 +3736,33 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Birgitta Wasstorp, Eva Grönlund</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112662551</t>
+          <t>https://artportalen.se/Sighting/128760310</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>82416825</v>
+        <v>112662551</v>
       </c>
       <c r="B31" t="n">
-        <v>87309</v>
+        <v>87412</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3764,40 +3770,36 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3674</v>
+        <v>3624</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lundås, Hallstavik, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>699838</v>
+        <v>699830</v>
       </c>
       <c r="R31" t="n">
-        <v>6660371</v>
+        <v>6660298</v>
       </c>
       <c r="S31" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3821,12 +3823,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2019-10-09</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2019-10-09</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3847,7 +3849,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Ossian Rydebjörk, Birgitta Wasstorp, Eva Grönlund</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3857,13 +3859,13 @@
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82416825</t>
+          <t>https://artportalen.se/Sighting/112662551</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>112662525</v>
+        <v>82416825</v>
       </c>
       <c r="B32" t="n">
         <v>87309</v>
@@ -3897,17 +3899,17 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Lundås, Hallstavik, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>699802</v>
+        <v>699838</v>
       </c>
       <c r="R32" t="n">
-        <v>6660244</v>
+        <v>6660371</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3931,12 +3933,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2019-10-09</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2019-10-09</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3957,7 +3959,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Birgitta Wasstorp, Eva Grönlund</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -3967,13 +3969,13 @@
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112662525</t>
+          <t>https://artportalen.se/Sighting/82416825</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>112662546</v>
+        <v>112662525</v>
       </c>
       <c r="B33" t="n">
         <v>87309</v>
@@ -4011,10 +4013,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>699830</v>
+        <v>699802</v>
       </c>
       <c r="R33" t="n">
-        <v>6660298</v>
+        <v>6660244</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4077,13 +4079,13 @@
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112662546</t>
+          <t>https://artportalen.se/Sighting/112662525</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>112662602</v>
+        <v>112662546</v>
       </c>
       <c r="B34" t="n">
         <v>87309</v>
@@ -4121,13 +4123,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>699809</v>
+        <v>699830</v>
       </c>
       <c r="R34" t="n">
-        <v>6660356</v>
+        <v>6660298</v>
       </c>
       <c r="S34" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4187,54 +4189,57 @@
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112662602</t>
+          <t>https://artportalen.se/Sighting/112662546</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128760336</v>
+        <v>112662602</v>
       </c>
       <c r="B35" t="n">
-        <v>87375</v>
+        <v>87309</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3739</v>
+        <v>3674</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>699835</v>
+        <v>699809</v>
       </c>
       <c r="R35" t="n">
-        <v>6660288</v>
+        <v>6660356</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4258,12 +4263,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4272,74 +4277,76 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Gillis Aronsson</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr"/>
+          <t>Ossian Rydebjörk, Birgitta Wasstorp, Eva Grönlund</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128760336</t>
+          <t>https://artportalen.se/Sighting/112662602</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>82416827</v>
+        <v>128760336</v>
       </c>
       <c r="B36" t="n">
-        <v>87146</v>
+        <v>87375</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3762</v>
+        <v>3739</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lundås, Hallstavik, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>699838</v>
+        <v>699835</v>
       </c>
       <c r="R36" t="n">
-        <v>6660371</v>
+        <v>6660288</v>
       </c>
       <c r="S36" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4363,12 +4370,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2019-10-09</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2019-10-09</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4377,35 +4384,30 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82416827</t>
+          <t>https://artportalen.se/Sighting/128760336</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>112662498</v>
+        <v>82416827</v>
       </c>
       <c r="B37" t="n">
         <v>87146</v>
@@ -4439,17 +4441,17 @@
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Lundås, Hallstavik, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>699752</v>
+        <v>699838</v>
       </c>
       <c r="R37" t="n">
-        <v>6660342</v>
+        <v>6660371</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4473,12 +4475,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2019-10-09</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2019-10-09</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4499,7 +4501,7 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Birgitta Wasstorp, Eva Grönlund</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4509,13 +4511,13 @@
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112662498</t>
+          <t>https://artportalen.se/Sighting/82416827</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128760311</v>
+        <v>112662498</v>
       </c>
       <c r="B38" t="n">
         <v>87146</v>
@@ -4544,19 +4546,22 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>699951</v>
+        <v>699752</v>
       </c>
       <c r="R38" t="n">
-        <v>6660298</v>
+        <v>6660342</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4580,12 +4585,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4594,30 +4599,35 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Gillis Aronsson</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr"/>
+          <t>Ossian Rydebjörk, Birgitta Wasstorp, Eva Grönlund</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128760311</t>
+          <t>https://artportalen.se/Sighting/112662498</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130379973</v>
+        <v>128760311</v>
       </c>
       <c r="B39" t="n">
         <v>87146</v>
@@ -4648,14 +4658,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Svedjan, SSV om Hallstavik, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>699820</v>
+        <v>699951</v>
       </c>
       <c r="R39" t="n">
-        <v>6660145</v>
+        <v>6660298</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4699,35 +4709,30 @@
       <c r="AG39" t="b">
         <v>0</v>
       </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>Äldre, grandominerad barrskog.</t>
-        </is>
-      </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Gillis Aronsson, Cajsa Björkén, Viktor Lund</t>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130379973</t>
+          <t>https://artportalen.se/Sighting/128760311</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124474451</v>
+        <v>130379973</v>
       </c>
       <c r="B40" t="n">
-        <v>91330</v>
+        <v>87146</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4735,37 +4740,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4189</v>
+        <v>3762</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Pers., nom.sanct</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Svedjan, SSV om Hallstavik, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>699943</v>
+        <v>699820</v>
       </c>
       <c r="R40" t="n">
-        <v>6660307</v>
+        <v>6660145</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4792,12 +4794,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4806,60 +4808,60 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Äldre, grandominerad barrskog.</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+          <t>Gillis Aronsson, Cajsa Björkén, Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124474451</t>
+          <t>https://artportalen.se/Sighting/130379973</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>82416822</v>
+        <v>124474451</v>
       </c>
       <c r="B41" t="n">
-        <v>93189</v>
+        <v>91330</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4361</v>
+        <v>4189</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Pers., nom.sanct</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4868,17 +4870,17 @@
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lundås, Hallstavik, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>699838</v>
+        <v>699943</v>
       </c>
       <c r="R41" t="n">
-        <v>6660371</v>
+        <v>6660307</v>
       </c>
       <c r="S41" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4902,12 +4904,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2019-10-09</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2019-10-09</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4923,12 +4925,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -4938,13 +4940,13 @@
       </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82416822</t>
+          <t>https://artportalen.se/Sighting/124474451</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>112662501</v>
+        <v>82416822</v>
       </c>
       <c r="B42" t="n">
         <v>93189</v>
@@ -4978,17 +4980,17 @@
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Lundås, Hallstavik, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>699752</v>
+        <v>699838</v>
       </c>
       <c r="R42" t="n">
-        <v>6660342</v>
+        <v>6660371</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5012,12 +5014,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2019-10-09</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2019-10-09</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5038,7 +5040,7 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Birgitta Wasstorp, Eva Grönlund</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -5048,13 +5050,13 @@
       </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112662501</t>
+          <t>https://artportalen.se/Sighting/82416822</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>112662567</v>
+        <v>112662501</v>
       </c>
       <c r="B43" t="n">
         <v>93189</v>
@@ -5092,13 +5094,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>699809</v>
+        <v>699752</v>
       </c>
       <c r="R43" t="n">
-        <v>6660356</v>
+        <v>6660342</v>
       </c>
       <c r="S43" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5158,13 +5160,13 @@
       </c>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112662567</t>
+          <t>https://artportalen.se/Sighting/112662501</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128760327</v>
+        <v>112662567</v>
       </c>
       <c r="B44" t="n">
         <v>93189</v>
@@ -5193,19 +5195,22 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>699826</v>
+        <v>699809</v>
       </c>
       <c r="R44" t="n">
-        <v>6660373</v>
+        <v>6660356</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5229,12 +5234,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5243,74 +5248,76 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Gillis Aronsson</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr"/>
+          <t>Ossian Rydebjörk, Birgitta Wasstorp, Eva Grönlund</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128760327</t>
+          <t>https://artportalen.se/Sighting/112662567</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>112662570</v>
+        <v>128760327</v>
       </c>
       <c r="B45" t="n">
-        <v>93193</v>
+        <v>93189</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4363</v>
+        <v>4361</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>699809</v>
+        <v>699826</v>
       </c>
       <c r="R45" t="n">
-        <v>6660356</v>
+        <v>6660373</v>
       </c>
       <c r="S45" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5334,12 +5341,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5348,60 +5355,55 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Birgitta Wasstorp, Eva Grönlund</t>
-        </is>
-      </c>
-      <c r="AY45" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112662570</t>
+          <t>https://artportalen.se/Sighting/128760327</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>112662568</v>
+        <v>112662570</v>
       </c>
       <c r="B46" t="n">
-        <v>93209</v>
+        <v>93193</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4366</v>
+        <v>4363</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5480,13 +5482,13 @@
       </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112662568</t>
+          <t>https://artportalen.se/Sighting/112662570</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128760313</v>
+        <v>112662568</v>
       </c>
       <c r="B47" t="n">
         <v>93209</v>
@@ -5515,19 +5517,22 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>699942</v>
+        <v>699809</v>
       </c>
       <c r="R47" t="n">
-        <v>6660292</v>
+        <v>6660356</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5551,12 +5556,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5565,30 +5570,35 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Gillis Aronsson</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr"/>
+          <t>Ossian Rydebjörk, Birgitta Wasstorp, Eva Grönlund</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128760313</t>
+          <t>https://artportalen.se/Sighting/112662568</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130379975</v>
+        <v>128760313</v>
       </c>
       <c r="B48" t="n">
         <v>93209</v>
@@ -5619,14 +5629,14 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Svedjan, SSV om Hallstavik, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>699783</v>
+        <v>699942</v>
       </c>
       <c r="R48" t="n">
-        <v>6660083</v>
+        <v>6660292</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5670,35 +5680,30 @@
       <c r="AG48" t="b">
         <v>0</v>
       </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>Äldre, grandominerad barrskog.</t>
-        </is>
-      </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Gillis Aronsson, Cajsa Björkén, Viktor Lund</t>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130379975</t>
+          <t>https://artportalen.se/Sighting/128760313</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>112662497</v>
+        <v>130379975</v>
       </c>
       <c r="B49" t="n">
-        <v>91424</v>
+        <v>93209</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5706,40 +5711,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5733</v>
+        <v>4366</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Såpfingersvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ramaria lutea</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Vent.) Schild</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Svedjan, SSV om Hallstavik, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>699752</v>
+        <v>699783</v>
       </c>
       <c r="R49" t="n">
-        <v>6660342</v>
+        <v>6660083</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5763,90 +5765,93 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF49" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>Äldre, grandominerad barrskog.</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Birgitta Wasstorp, Eva Grönlund</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+          <t>Gillis Aronsson, Cajsa Björkén, Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112662497</t>
+          <t>https://artportalen.se/Sighting/130379975</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128760322</v>
+        <v>112662497</v>
       </c>
       <c r="B50" t="n">
-        <v>91398</v>
+        <v>91424</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5745</v>
+        <v>5733</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gyllenfingersvamp</t>
+          <t>Såpfingersvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Ramaria brunneicontusa</t>
+          <t>Ramaria lutea</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Vent.) Schild</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>699806</v>
+        <v>699752</v>
       </c>
       <c r="R50" t="n">
-        <v>6660365</v>
+        <v>6660342</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5870,88 +5875,90 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Gillis Aronsson</t>
-        </is>
-      </c>
-      <c r="AY50" t="inlineStr"/>
+          <t>Ossian Rydebjörk, Birgitta Wasstorp, Eva Grönlund</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128760322</t>
+          <t>https://artportalen.se/Sighting/112662497</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>112662544</v>
+        <v>128760322</v>
       </c>
       <c r="B51" t="n">
-        <v>91435</v>
+        <v>91398</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5747</v>
+        <v>5745</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Gyllenfingersvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Ramaria brunneicontusa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>699830</v>
+        <v>699806</v>
       </c>
       <c r="R51" t="n">
-        <v>6660298</v>
+        <v>6660365</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5975,12 +5982,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5989,35 +5996,30 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Birgitta Wasstorp, Eva Grönlund</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112662544</t>
+          <t>https://artportalen.se/Sighting/128760322</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128760320</v>
+        <v>112662544</v>
       </c>
       <c r="B52" t="n">
         <v>91435</v>
@@ -6046,19 +6048,22 @@
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>699820</v>
+        <v>699830</v>
       </c>
       <c r="R52" t="n">
         <v>6660298</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6082,12 +6087,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6096,55 +6101,60 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Gillis Aronsson</t>
-        </is>
-      </c>
-      <c r="AY52" t="inlineStr"/>
+          <t>Ossian Rydebjörk, Birgitta Wasstorp, Eva Grönlund</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128760320</t>
+          <t>https://artportalen.se/Sighting/112662544</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128760334</v>
+        <v>128760320</v>
       </c>
       <c r="B53" t="n">
-        <v>92928</v>
+        <v>91435</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5836</v>
+        <v>5747</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Guldkremla</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Russula aurea</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Pers.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6154,10 +6164,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>699664</v>
+        <v>699820</v>
       </c>
       <c r="R53" t="n">
-        <v>6660365</v>
+        <v>6660298</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6215,54 +6225,54 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128760334</t>
+          <t>https://artportalen.se/Sighting/128760320</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124444432</v>
+        <v>128760334</v>
       </c>
       <c r="B54" t="n">
-        <v>93233</v>
+        <v>92928</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5964</v>
+        <v>5836</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Guldkremla</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Russula aurea</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Pers.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>699938</v>
+        <v>699664</v>
       </c>
       <c r="R54" t="n">
-        <v>6660298</v>
+        <v>6660365</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6286,12 +6296,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6306,24 +6316,24 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124444432</t>
+          <t>https://artportalen.se/Sighting/128760334</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124445128</v>
+        <v>124444432</v>
       </c>
       <c r="B55" t="n">
         <v>93233</v>
@@ -6358,13 +6368,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>699954</v>
+        <v>699938</v>
       </c>
       <c r="R55" t="n">
-        <v>6660370</v>
+        <v>6660298</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6419,13 +6429,13 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124445128</t>
+          <t>https://artportalen.se/Sighting/124444432</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128760312</v>
+        <v>124445128</v>
       </c>
       <c r="B56" t="n">
         <v>93233</v>
@@ -6456,14 +6466,14 @@
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>699945</v>
+        <v>699954</v>
       </c>
       <c r="R56" t="n">
-        <v>6660298</v>
+        <v>6660370</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6490,12 +6500,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6510,70 +6520,65 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Gillis Aronsson</t>
+          <t>Viktor Lund, Martin Axegård</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128760312</t>
+          <t>https://artportalen.se/Sighting/124445128</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124449907</v>
+        <v>128760312</v>
       </c>
       <c r="B57" t="n">
-        <v>57950</v>
+        <v>93233</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>5964</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>699754</v>
+        <v>699945</v>
       </c>
       <c r="R57" t="n">
-        <v>6660376</v>
+        <v>6660298</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6597,12 +6602,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6617,70 +6622,65 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124449907</t>
+          <t>https://artportalen.se/Sighting/128760312</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124451081</v>
+        <v>136644437</v>
       </c>
       <c r="B58" t="n">
-        <v>57950</v>
+        <v>93436</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>5964</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>699683</v>
+        <v>699790</v>
       </c>
       <c r="R58" t="n">
-        <v>6660350</v>
+        <v>6660268</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6704,12 +6704,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6724,24 +6734,24 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124451081</t>
+          <t>https://artportalen.se/Sighting/136644437</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130379971</v>
+        <v>124449907</v>
       </c>
       <c r="B59" t="n">
         <v>57950</v>
@@ -6769,11 +6779,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
           <t>lockläte, övriga läten</t>
@@ -6781,17 +6787,17 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Svedjan, SSV om Hallstavik, Upl</t>
+          <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>699710</v>
+        <v>699754</v>
       </c>
       <c r="R59" t="n">
-        <v>6660225</v>
+        <v>6660376</v>
       </c>
       <c r="S59" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6815,12 +6821,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6831,36 +6837,31 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AI59" t="inlineStr">
-        <is>
-          <t>Äldre, grandominerad barrskog.</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Gillis Aronsson, Cajsa Björkén</t>
+          <t>Viktor Lund, Martin Axegård</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130379971</t>
+          <t>https://artportalen.se/Sighting/124449907</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124445043</v>
+        <v>124451081</v>
       </c>
       <c r="B60" t="n">
-        <v>5179</v>
+        <v>57950</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6868,27 +6869,27 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -6897,10 +6898,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>699954</v>
+        <v>699683</v>
       </c>
       <c r="R60" t="n">
-        <v>6660370</v>
+        <v>6660350</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6958,16 +6959,16 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124445043</t>
+          <t>https://artportalen.se/Sighting/124451081</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124447074</v>
+        <v>130379971</v>
       </c>
       <c r="B61" t="n">
-        <v>5179</v>
+        <v>57950</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6975,42 +6976,46 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Svedjan, SSV om Hallstavik, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>699804</v>
+        <v>699710</v>
       </c>
       <c r="R61" t="n">
-        <v>6660392</v>
+        <v>6660225</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7034,12 +7039,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7050,31 +7055,36 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>Äldre, grandominerad barrskog.</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
+          <t>Gillis Aronsson, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124447074</t>
+          <t>https://artportalen.se/Sighting/130379971</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124444974</v>
+        <v>124445043</v>
       </c>
       <c r="B62" t="n">
-        <v>5199</v>
+        <v>5179</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7082,21 +7092,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7172,16 +7182,16 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124444974</t>
+          <t>https://artportalen.se/Sighting/124445043</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>105298082</v>
+        <v>124447074</v>
       </c>
       <c r="B63" t="n">
-        <v>99096</v>
+        <v>5179</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7189,34 +7199,39 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>219798</v>
+        <v>100526</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>699586</v>
+        <v>699804</v>
       </c>
       <c r="R63" t="n">
-        <v>6660420</v>
+        <v>6660392</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7243,12 +7258,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2022-10-10</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2022-10-10</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7263,27 +7278,27 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Viktor Lund, Martin Axegård</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/105298082</t>
+          <t>https://artportalen.se/Sighting/124447074</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>105298083</v>
+        <v>136644428</v>
       </c>
       <c r="B64" t="n">
-        <v>99096</v>
+        <v>4783</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7291,21 +7306,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>219798</v>
+        <v>102306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7315,13 +7330,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>699594</v>
+        <v>699947</v>
       </c>
       <c r="R64" t="n">
-        <v>6660387</v>
+        <v>6660329</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7345,12 +7360,22 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2022-10-10</t>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2022-10-10</t>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7365,27 +7390,27 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/105298083</t>
+          <t>https://artportalen.se/Sighting/136644428</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>105298085</v>
+        <v>136644432</v>
       </c>
       <c r="B65" t="n">
-        <v>99096</v>
+        <v>4783</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7393,21 +7418,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>219798</v>
+        <v>102306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7417,13 +7442,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>699604</v>
+        <v>699856</v>
       </c>
       <c r="R65" t="n">
-        <v>6660405</v>
+        <v>6660318</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7447,12 +7472,22 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2022-10-10</t>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2022-10-10</t>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7467,59 +7502,55 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/105298085</t>
+          <t>https://artportalen.se/Sighting/136644432</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124447516</v>
+        <v>124444974</v>
       </c>
       <c r="B66" t="n">
-        <v>99118</v>
+        <v>5199</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -7528,10 +7559,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>699800</v>
+        <v>699954</v>
       </c>
       <c r="R66" t="n">
-        <v>6660415</v>
+        <v>6660370</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7589,16 +7620,16 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124447516</t>
+          <t>https://artportalen.se/Sighting/124444974</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124454215</v>
+        <v>105298082</v>
       </c>
       <c r="B67" t="n">
-        <v>97983</v>
+        <v>99096</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7606,37 +7637,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221945</v>
+        <v>219798</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>699929</v>
+        <v>699586</v>
       </c>
       <c r="R67" t="n">
-        <v>6660329</v>
+        <v>6660420</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7660,12 +7691,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2022-10-10</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2022-10-10</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7680,27 +7711,27 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Niina Sallmén</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
+          <t>Niina Sallmén</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124454215</t>
+          <t>https://artportalen.se/Sighting/105298082</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>105298080</v>
+        <v>105298083</v>
       </c>
       <c r="B68" t="n">
-        <v>101326</v>
+        <v>99096</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7708,21 +7739,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7732,10 +7763,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>699598</v>
+        <v>699594</v>
       </c>
       <c r="R68" t="n">
-        <v>6660467</v>
+        <v>6660387</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7793,16 +7824,16 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/105298080</t>
+          <t>https://artportalen.se/Sighting/105298083</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124444956</v>
+        <v>105298085</v>
       </c>
       <c r="B69" t="n">
-        <v>101326</v>
+        <v>99096</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7810,37 +7841,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>699944</v>
+        <v>699604</v>
       </c>
       <c r="R69" t="n">
-        <v>6660374</v>
+        <v>6660405</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7864,12 +7895,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2022-10-10</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2022-10-10</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7884,65 +7915,74 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Niina Sallmén</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
+          <t>Niina Sallmén</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124444956</t>
+          <t>https://artportalen.se/Sighting/105298085</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124446528</v>
+        <v>124447516</v>
       </c>
       <c r="B70" t="n">
-        <v>101326</v>
+        <v>99118</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>699808</v>
+        <v>699800</v>
       </c>
       <c r="R70" t="n">
-        <v>6660347</v>
+        <v>6660415</v>
       </c>
       <c r="S70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7997,16 +8037,16 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124446528</t>
+          <t>https://artportalen.se/Sighting/124447516</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124450248</v>
+        <v>124454215</v>
       </c>
       <c r="B71" t="n">
-        <v>101326</v>
+        <v>97983</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8014,21 +8054,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8038,10 +8078,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>699796</v>
+        <v>699929</v>
       </c>
       <c r="R71" t="n">
-        <v>6660315</v>
+        <v>6660329</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -8099,13 +8139,13 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124450248</t>
+          <t>https://artportalen.se/Sighting/124454215</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124451595</v>
+        <v>105298080</v>
       </c>
       <c r="B72" t="n">
         <v>101326</v>
@@ -8136,14 +8176,14 @@
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>699683</v>
+        <v>699598</v>
       </c>
       <c r="R72" t="n">
-        <v>6660350</v>
+        <v>6660467</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8170,12 +8210,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2022-10-10</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2022-10-10</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8190,24 +8230,24 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Niina Sallmén</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
+          <t>Niina Sallmén</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124451595</t>
+          <t>https://artportalen.se/Sighting/105298080</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124452710</v>
+        <v>124444956</v>
       </c>
       <c r="B73" t="n">
         <v>101326</v>
@@ -8242,10 +8282,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>699855</v>
+        <v>699944</v>
       </c>
       <c r="R73" t="n">
-        <v>6660145</v>
+        <v>6660374</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -8303,13 +8343,13 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124452710</t>
+          <t>https://artportalen.se/Sighting/124444956</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124474452</v>
+        <v>124446528</v>
       </c>
       <c r="B74" t="n">
         <v>101326</v>
@@ -8340,17 +8380,17 @@
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>699807</v>
+        <v>699808</v>
       </c>
       <c r="R74" t="n">
-        <v>6660377</v>
+        <v>6660347</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8394,24 +8434,24 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Martin Axegård</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124474452</t>
+          <t>https://artportalen.se/Sighting/124446528</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124474453</v>
+        <v>124450248</v>
       </c>
       <c r="B75" t="n">
         <v>101326</v>
@@ -8442,17 +8482,17 @@
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>699934</v>
+        <v>699796</v>
       </c>
       <c r="R75" t="n">
-        <v>6660275</v>
+        <v>6660315</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8496,62 +8536,62 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Martin Axegård</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124474453</t>
+          <t>https://artportalen.se/Sighting/124450248</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>105298081</v>
+        <v>124451595</v>
       </c>
       <c r="B76" t="n">
-        <v>103403</v>
+        <v>101326</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>223246</v>
+        <v>222498</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>699637</v>
+        <v>699683</v>
       </c>
       <c r="R76" t="n">
-        <v>6660447</v>
+        <v>6660350</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8578,17 +8618,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2022-10-10</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2022-10-10</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>ungt träd</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8603,65 +8638,65 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Viktor Lund, Martin Axegård</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/105298081</t>
+          <t>https://artportalen.se/Sighting/124451595</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>105298084</v>
+        <v>124452710</v>
       </c>
       <c r="B77" t="n">
-        <v>103403</v>
+        <v>101326</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>223246</v>
+        <v>222498</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>699592</v>
+        <v>699855</v>
       </c>
       <c r="R77" t="n">
-        <v>6660391</v>
+        <v>6660145</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8685,17 +8720,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2022-10-10</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2022-10-10</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>flera unga träd</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8710,49 +8740,49 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Viktor Lund, Martin Axegård</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/105298084</t>
+          <t>https://artportalen.se/Sighting/124452710</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>105298088</v>
+        <v>124474452</v>
       </c>
       <c r="B78" t="n">
-        <v>103403</v>
+        <v>101326</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>223246</v>
+        <v>222498</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8762,10 +8792,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>699655</v>
+        <v>699807</v>
       </c>
       <c r="R78" t="n">
-        <v>6660307</v>
+        <v>6660377</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8792,17 +8822,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2022-10-10</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2022-10-10</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>ungt träd</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8817,49 +8842,49 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/105298088</t>
+          <t>https://artportalen.se/Sighting/124474452</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>105298089</v>
+        <v>124474453</v>
       </c>
       <c r="B79" t="n">
-        <v>103403</v>
+        <v>101326</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>223246</v>
+        <v>222498</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8869,10 +8894,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>699671</v>
+        <v>699934</v>
       </c>
       <c r="R79" t="n">
-        <v>6660294</v>
+        <v>6660275</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8899,17 +8924,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2022-10-10</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2022-10-10</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>ett par stycken ganska unga träd</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8924,49 +8944,49 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/105298089</t>
+          <t>https://artportalen.se/Sighting/124474453</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>105298090</v>
+        <v>136644422</v>
       </c>
       <c r="B80" t="n">
-        <v>103403</v>
+        <v>101552</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>223246</v>
+        <v>222498</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8976,13 +8996,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>699721</v>
+        <v>699910</v>
       </c>
       <c r="R80" t="n">
-        <v>6660259</v>
+        <v>6660374</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9006,17 +9026,22 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2022-10-10</t>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2022-10-10</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>ungt träd</t>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9031,68 +9056,65 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/105298090</t>
+          <t>https://artportalen.se/Sighting/136644422</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>112662524</v>
+        <v>136644430</v>
       </c>
       <c r="B81" t="n">
-        <v>92688</v>
+        <v>101552</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>232138</v>
+        <v>222498</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Gul lammticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Albatrellus citrinus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Ryman</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>699802</v>
+        <v>699943</v>
       </c>
       <c r="R81" t="n">
-        <v>6660244</v>
+        <v>6660327</v>
       </c>
       <c r="S81" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9116,12 +9138,22 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9130,60 +9162,55 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Birgitta Wasstorp, Eva Grönlund</t>
-        </is>
-      </c>
-      <c r="AY81" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112662524</t>
+          <t>https://artportalen.se/Sighting/136644430</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128760332</v>
+        <v>136644431</v>
       </c>
       <c r="B82" t="n">
-        <v>92688</v>
+        <v>101552</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>232138</v>
+        <v>222498</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Gul lammticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Albatrellus citrinus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Ryman</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9193,13 +9220,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>699706</v>
+        <v>699947</v>
       </c>
       <c r="R82" t="n">
-        <v>6660389</v>
+        <v>6660312</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9223,12 +9250,22 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9243,16 +9280,1211 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Gillis Aronsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136644431</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>136644434</v>
+      </c>
+      <c r="B83" t="n">
+        <v>101552</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Lundås, Upl</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>699842</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6660319</v>
+      </c>
+      <c r="S83" t="n">
+        <v>5</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136644434</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>136644435</v>
+      </c>
+      <c r="B84" t="n">
+        <v>101552</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Lundås, Upl</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>699842</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6660285</v>
+      </c>
+      <c r="S84" t="n">
+        <v>5</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136644435</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>136644436</v>
+      </c>
+      <c r="B85" t="n">
+        <v>101552</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Lundås, Upl</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>699794</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6660269</v>
+      </c>
+      <c r="S85" t="n">
+        <v>5</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136644436</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>136644439</v>
+      </c>
+      <c r="B86" t="n">
+        <v>101552</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Lundås, Upl</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>699782</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6660269</v>
+      </c>
+      <c r="S86" t="n">
+        <v>5</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136644439</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>105298081</v>
+      </c>
+      <c r="B87" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Lundås, Upl</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>699637</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6660447</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2022-10-10</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2022-10-10</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>ungt träd</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105298081</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>105298084</v>
+      </c>
+      <c r="B88" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Lundås, Upl</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>699592</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6660391</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2022-10-10</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2022-10-10</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>flera unga träd</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105298084</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>105298088</v>
+      </c>
+      <c r="B89" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Lundås, Upl</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>699655</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6660307</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2022-10-10</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2022-10-10</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>ungt träd</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105298088</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>105298089</v>
+      </c>
+      <c r="B90" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Lundås, Upl</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>699671</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6660294</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2022-10-10</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2022-10-10</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>ett par stycken ganska unga träd</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105298089</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>105298090</v>
+      </c>
+      <c r="B91" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Lundås, Upl</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>699721</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6660259</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2022-10-10</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2022-10-10</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>ungt träd</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105298090</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>112662524</v>
+      </c>
+      <c r="B92" t="n">
+        <v>92688</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>232138</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Gul lammticka</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Albatrellus citrinus</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Ryman</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Lundås, Upl</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>699802</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6660244</v>
+      </c>
+      <c r="S92" t="n">
+        <v>25</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2023-10-11</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2023-10-11</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF92" t="inlineStr"/>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Ossian Rydebjörk</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Ossian Rydebjörk, Birgitta Wasstorp, Eva Grönlund</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112662524</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>128760332</v>
+      </c>
+      <c r="B93" t="n">
+        <v>92688</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>232138</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Gul lammticka</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Albatrellus citrinus</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Ryman</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Lundås, Upl</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>699706</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6660389</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/128760332</t>
         </is>
@@ -9341,6 +10573,17 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 17406-2025 artfynd.xlsx
+++ b/artfynd/A 17406-2025 artfynd.xlsx
@@ -3339,7 +3339,7 @@
         <v>136644424</v>
       </c>
       <c r="B27" t="n">
-        <v>96554</v>
+        <v>96557</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -6642,7 +6642,7 @@
         <v>136644437</v>
       </c>
       <c r="B58" t="n">
-        <v>93436</v>
+        <v>93439</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -8964,7 +8964,7 @@
         <v>136644422</v>
       </c>
       <c r="B80" t="n">
-        <v>101552</v>
+        <v>101555</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         <v>136644430</v>
       </c>
       <c r="B81" t="n">
-        <v>101552</v>
+        <v>101555</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9188,7 +9188,7 @@
         <v>136644431</v>
       </c>
       <c r="B82" t="n">
-        <v>101552</v>
+        <v>101555</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9300,7 +9300,7 @@
         <v>136644434</v>
       </c>
       <c r="B83" t="n">
-        <v>101552</v>
+        <v>101555</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9412,7 +9412,7 @@
         <v>136644435</v>
       </c>
       <c r="B84" t="n">
-        <v>101552</v>
+        <v>101555</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9524,7 +9524,7 @@
         <v>136644436</v>
       </c>
       <c r="B85" t="n">
-        <v>101552</v>
+        <v>101555</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9636,7 +9636,7 @@
         <v>136644439</v>
       </c>
       <c r="B86" t="n">
-        <v>101552</v>
+        <v>101555</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>

--- a/artfynd/A 17406-2025 artfynd.xlsx
+++ b/artfynd/A 17406-2025 artfynd.xlsx
@@ -3339,7 +3339,7 @@
         <v>136644424</v>
       </c>
       <c r="B27" t="n">
-        <v>96557</v>
+        <v>96558</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -6642,7 +6642,7 @@
         <v>136644437</v>
       </c>
       <c r="B58" t="n">
-        <v>93439</v>
+        <v>93440</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -8964,7 +8964,7 @@
         <v>136644422</v>
       </c>
       <c r="B80" t="n">
-        <v>101555</v>
+        <v>101556</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         <v>136644430</v>
       </c>
       <c r="B81" t="n">
-        <v>101555</v>
+        <v>101556</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9188,7 +9188,7 @@
         <v>136644431</v>
       </c>
       <c r="B82" t="n">
-        <v>101555</v>
+        <v>101556</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9300,7 +9300,7 @@
         <v>136644434</v>
       </c>
       <c r="B83" t="n">
-        <v>101555</v>
+        <v>101556</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9412,7 +9412,7 @@
         <v>136644435</v>
       </c>
       <c r="B84" t="n">
-        <v>101555</v>
+        <v>101556</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9524,7 +9524,7 @@
         <v>136644436</v>
       </c>
       <c r="B85" t="n">
-        <v>101555</v>
+        <v>101556</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9636,7 +9636,7 @@
         <v>136644439</v>
       </c>
       <c r="B86" t="n">
-        <v>101555</v>
+        <v>101556</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>

--- a/artfynd/A 17406-2025 artfynd.xlsx
+++ b/artfynd/A 17406-2025 artfynd.xlsx
@@ -3439,7 +3439,11 @@
           <t>Tomas Falk</t>
         </is>
       </c>
-      <c r="AY27" t="inlineStr"/>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Upplands kalkbarrskogar</t>
+        </is>
+      </c>
       <c r="AZ27" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136644424</t>
@@ -6742,7 +6746,11 @@
           <t>Tomas Falk</t>
         </is>
       </c>
-      <c r="AY58" t="inlineStr"/>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>Upplands kalkbarrskogar</t>
+        </is>
+      </c>
       <c r="AZ58" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136644437</t>
@@ -7398,7 +7406,11 @@
           <t>Tomas Falk</t>
         </is>
       </c>
-      <c r="AY64" t="inlineStr"/>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>Upplands kalkbarrskogar</t>
+        </is>
+      </c>
       <c r="AZ64" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136644428</t>
@@ -7510,7 +7522,11 @@
           <t>Tomas Falk</t>
         </is>
       </c>
-      <c r="AY65" t="inlineStr"/>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>Upplands kalkbarrskogar</t>
+        </is>
+      </c>
       <c r="AZ65" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136644432</t>
@@ -9064,7 +9080,11 @@
           <t>Tomas Falk</t>
         </is>
       </c>
-      <c r="AY80" t="inlineStr"/>
+      <c r="AY80" t="inlineStr">
+        <is>
+          <t>Upplands kalkbarrskogar</t>
+        </is>
+      </c>
       <c r="AZ80" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136644422</t>
@@ -9176,7 +9196,11 @@
           <t>Tomas Falk</t>
         </is>
       </c>
-      <c r="AY81" t="inlineStr"/>
+      <c r="AY81" t="inlineStr">
+        <is>
+          <t>Upplands kalkbarrskogar</t>
+        </is>
+      </c>
       <c r="AZ81" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136644430</t>
@@ -9288,7 +9312,11 @@
           <t>Tomas Falk</t>
         </is>
       </c>
-      <c r="AY82" t="inlineStr"/>
+      <c r="AY82" t="inlineStr">
+        <is>
+          <t>Upplands kalkbarrskogar</t>
+        </is>
+      </c>
       <c r="AZ82" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136644431</t>
@@ -9400,7 +9428,11 @@
           <t>Tomas Falk</t>
         </is>
       </c>
-      <c r="AY83" t="inlineStr"/>
+      <c r="AY83" t="inlineStr">
+        <is>
+          <t>Upplands kalkbarrskogar</t>
+        </is>
+      </c>
       <c r="AZ83" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136644434</t>
@@ -9512,7 +9544,11 @@
           <t>Tomas Falk</t>
         </is>
       </c>
-      <c r="AY84" t="inlineStr"/>
+      <c r="AY84" t="inlineStr">
+        <is>
+          <t>Upplands kalkbarrskogar</t>
+        </is>
+      </c>
       <c r="AZ84" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136644435</t>
@@ -9624,7 +9660,11 @@
           <t>Tomas Falk</t>
         </is>
       </c>
-      <c r="AY85" t="inlineStr"/>
+      <c r="AY85" t="inlineStr">
+        <is>
+          <t>Upplands kalkbarrskogar</t>
+        </is>
+      </c>
       <c r="AZ85" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136644436</t>
@@ -9736,7 +9776,11 @@
           <t>Tomas Falk</t>
         </is>
       </c>
-      <c r="AY86" t="inlineStr"/>
+      <c r="AY86" t="inlineStr">
+        <is>
+          <t>Upplands kalkbarrskogar</t>
+        </is>
+      </c>
       <c r="AZ86" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136644439</t>

--- a/artfynd/A 17406-2025 artfynd.xlsx
+++ b/artfynd/A 17406-2025 artfynd.xlsx
@@ -3339,7 +3339,7 @@
         <v>136644424</v>
       </c>
       <c r="B27" t="n">
-        <v>96558</v>
+        <v>96563</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -6646,7 +6646,7 @@
         <v>136644437</v>
       </c>
       <c r="B58" t="n">
-        <v>93440</v>
+        <v>93445</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -8980,7 +8980,7 @@
         <v>136644422</v>
       </c>
       <c r="B80" t="n">
-        <v>101556</v>
+        <v>101561</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
         <v>136644430</v>
       </c>
       <c r="B81" t="n">
-        <v>101556</v>
+        <v>101561</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9212,7 +9212,7 @@
         <v>136644431</v>
       </c>
       <c r="B82" t="n">
-        <v>101556</v>
+        <v>101561</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9328,7 +9328,7 @@
         <v>136644434</v>
       </c>
       <c r="B83" t="n">
-        <v>101556</v>
+        <v>101561</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9444,7 +9444,7 @@
         <v>136644435</v>
       </c>
       <c r="B84" t="n">
-        <v>101556</v>
+        <v>101561</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         <v>136644436</v>
       </c>
       <c r="B85" t="n">
-        <v>101556</v>
+        <v>101561</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9676,7 +9676,7 @@
         <v>136644439</v>
       </c>
       <c r="B86" t="n">
-        <v>101556</v>
+        <v>101561</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>

--- a/artfynd/A 17406-2025 artfynd.xlsx
+++ b/artfynd/A 17406-2025 artfynd.xlsx
@@ -3339,7 +3339,7 @@
         <v>136644424</v>
       </c>
       <c r="B27" t="n">
-        <v>96563</v>
+        <v>96565</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -6646,7 +6646,7 @@
         <v>136644437</v>
       </c>
       <c r="B58" t="n">
-        <v>93445</v>
+        <v>93447</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -8980,7 +8980,7 @@
         <v>136644422</v>
       </c>
       <c r="B80" t="n">
-        <v>101561</v>
+        <v>101563</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
         <v>136644430</v>
       </c>
       <c r="B81" t="n">
-        <v>101561</v>
+        <v>101563</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9212,7 +9212,7 @@
         <v>136644431</v>
       </c>
       <c r="B82" t="n">
-        <v>101561</v>
+        <v>101563</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9328,7 +9328,7 @@
         <v>136644434</v>
       </c>
       <c r="B83" t="n">
-        <v>101561</v>
+        <v>101563</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9444,7 +9444,7 @@
         <v>136644435</v>
       </c>
       <c r="B84" t="n">
-        <v>101561</v>
+        <v>101563</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         <v>136644436</v>
       </c>
       <c r="B85" t="n">
-        <v>101561</v>
+        <v>101563</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9676,7 +9676,7 @@
         <v>136644439</v>
       </c>
       <c r="B86" t="n">
-        <v>101561</v>
+        <v>101563</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>

--- a/artfynd/A 17406-2025 artfynd.xlsx
+++ b/artfynd/A 17406-2025 artfynd.xlsx
@@ -3339,7 +3339,7 @@
         <v>136644424</v>
       </c>
       <c r="B27" t="n">
-        <v>96565</v>
+        <v>96571</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -6646,7 +6646,7 @@
         <v>136644437</v>
       </c>
       <c r="B58" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -8980,7 +8980,7 @@
         <v>136644422</v>
       </c>
       <c r="B80" t="n">
-        <v>101563</v>
+        <v>101569</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
         <v>136644430</v>
       </c>
       <c r="B81" t="n">
-        <v>101563</v>
+        <v>101569</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9212,7 +9212,7 @@
         <v>136644431</v>
       </c>
       <c r="B82" t="n">
-        <v>101563</v>
+        <v>101569</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9328,7 +9328,7 @@
         <v>136644434</v>
       </c>
       <c r="B83" t="n">
-        <v>101563</v>
+        <v>101569</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9444,7 +9444,7 @@
         <v>136644435</v>
       </c>
       <c r="B84" t="n">
-        <v>101563</v>
+        <v>101569</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         <v>136644436</v>
       </c>
       <c r="B85" t="n">
-        <v>101563</v>
+        <v>101569</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9676,7 +9676,7 @@
         <v>136644439</v>
       </c>
       <c r="B86" t="n">
-        <v>101563</v>
+        <v>101569</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>

--- a/artfynd/A 17406-2025 artfynd.xlsx
+++ b/artfynd/A 17406-2025 artfynd.xlsx
@@ -3339,7 +3339,7 @@
         <v>136644424</v>
       </c>
       <c r="B27" t="n">
-        <v>96571</v>
+        <v>96573</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -6646,7 +6646,7 @@
         <v>136644437</v>
       </c>
       <c r="B58" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -8980,7 +8980,7 @@
         <v>136644422</v>
       </c>
       <c r="B80" t="n">
-        <v>101569</v>
+        <v>101571</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
         <v>136644430</v>
       </c>
       <c r="B81" t="n">
-        <v>101569</v>
+        <v>101571</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9212,7 +9212,7 @@
         <v>136644431</v>
       </c>
       <c r="B82" t="n">
-        <v>101569</v>
+        <v>101571</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9328,7 +9328,7 @@
         <v>136644434</v>
       </c>
       <c r="B83" t="n">
-        <v>101569</v>
+        <v>101571</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9444,7 +9444,7 @@
         <v>136644435</v>
       </c>
       <c r="B84" t="n">
-        <v>101569</v>
+        <v>101571</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         <v>136644436</v>
       </c>
       <c r="B85" t="n">
-        <v>101569</v>
+        <v>101571</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9676,7 +9676,7 @@
         <v>136644439</v>
       </c>
       <c r="B86" t="n">
-        <v>101569</v>
+        <v>101571</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>

--- a/artfynd/A 17406-2025 artfynd.xlsx
+++ b/artfynd/A 17406-2025 artfynd.xlsx
@@ -3339,7 +3339,7 @@
         <v>136644424</v>
       </c>
       <c r="B27" t="n">
-        <v>96573</v>
+        <v>96574</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -6646,7 +6646,7 @@
         <v>136644437</v>
       </c>
       <c r="B58" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -8980,7 +8980,7 @@
         <v>136644422</v>
       </c>
       <c r="B80" t="n">
-        <v>101571</v>
+        <v>101572</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
         <v>136644430</v>
       </c>
       <c r="B81" t="n">
-        <v>101571</v>
+        <v>101572</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9212,7 +9212,7 @@
         <v>136644431</v>
       </c>
       <c r="B82" t="n">
-        <v>101571</v>
+        <v>101572</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9328,7 +9328,7 @@
         <v>136644434</v>
       </c>
       <c r="B83" t="n">
-        <v>101571</v>
+        <v>101572</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9444,7 +9444,7 @@
         <v>136644435</v>
       </c>
       <c r="B84" t="n">
-        <v>101571</v>
+        <v>101572</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         <v>136644436</v>
       </c>
       <c r="B85" t="n">
-        <v>101571</v>
+        <v>101572</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9676,7 +9676,7 @@
         <v>136644439</v>
       </c>
       <c r="B86" t="n">
-        <v>101571</v>
+        <v>101572</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>

--- a/artfynd/A 17406-2025 artfynd.xlsx
+++ b/artfynd/A 17406-2025 artfynd.xlsx
@@ -3339,7 +3339,7 @@
         <v>136644424</v>
       </c>
       <c r="B27" t="n">
-        <v>96574</v>
+        <v>96580</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -6646,7 +6646,7 @@
         <v>136644437</v>
       </c>
       <c r="B58" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -8980,7 +8980,7 @@
         <v>136644422</v>
       </c>
       <c r="B80" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
         <v>136644430</v>
       </c>
       <c r="B81" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9212,7 +9212,7 @@
         <v>136644431</v>
       </c>
       <c r="B82" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9328,7 +9328,7 @@
         <v>136644434</v>
       </c>
       <c r="B83" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9444,7 +9444,7 @@
         <v>136644435</v>
       </c>
       <c r="B84" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         <v>136644436</v>
       </c>
       <c r="B85" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9676,7 +9676,7 @@
         <v>136644439</v>
       </c>
       <c r="B86" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>

--- a/artfynd/A 17406-2025 artfynd.xlsx
+++ b/artfynd/A 17406-2025 artfynd.xlsx
@@ -3339,7 +3339,7 @@
         <v>136644424</v>
       </c>
       <c r="B27" t="n">
-        <v>96580</v>
+        <v>96584</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -6646,7 +6646,7 @@
         <v>136644437</v>
       </c>
       <c r="B58" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -8980,7 +8980,7 @@
         <v>136644422</v>
       </c>
       <c r="B80" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
         <v>136644430</v>
       </c>
       <c r="B81" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9212,7 +9212,7 @@
         <v>136644431</v>
       </c>
       <c r="B82" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9328,7 +9328,7 @@
         <v>136644434</v>
       </c>
       <c r="B83" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9444,7 +9444,7 @@
         <v>136644435</v>
       </c>
       <c r="B84" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         <v>136644436</v>
       </c>
       <c r="B85" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9676,7 +9676,7 @@
         <v>136644439</v>
       </c>
       <c r="B86" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>

--- a/artfynd/A 17406-2025 artfynd.xlsx
+++ b/artfynd/A 17406-2025 artfynd.xlsx
@@ -3339,7 +3339,7 @@
         <v>136644424</v>
       </c>
       <c r="B27" t="n">
-        <v>96584</v>
+        <v>96586</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -8980,7 +8980,7 @@
         <v>136644422</v>
       </c>
       <c r="B80" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
         <v>136644430</v>
       </c>
       <c r="B81" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9212,7 +9212,7 @@
         <v>136644431</v>
       </c>
       <c r="B82" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9328,7 +9328,7 @@
         <v>136644434</v>
       </c>
       <c r="B83" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9444,7 +9444,7 @@
         <v>136644435</v>
       </c>
       <c r="B84" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         <v>136644436</v>
       </c>
       <c r="B85" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9676,7 +9676,7 @@
         <v>136644439</v>
       </c>
       <c r="B86" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>

--- a/artfynd/A 17406-2025 artfynd.xlsx
+++ b/artfynd/A 17406-2025 artfynd.xlsx
@@ -3339,7 +3339,7 @@
         <v>136644424</v>
       </c>
       <c r="B27" t="n">
-        <v>96586</v>
+        <v>96588</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -6646,7 +6646,7 @@
         <v>136644437</v>
       </c>
       <c r="B58" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -8980,7 +8980,7 @@
         <v>136644422</v>
       </c>
       <c r="B80" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
         <v>136644430</v>
       </c>
       <c r="B81" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9212,7 +9212,7 @@
         <v>136644431</v>
       </c>
       <c r="B82" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9328,7 +9328,7 @@
         <v>136644434</v>
       </c>
       <c r="B83" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9444,7 +9444,7 @@
         <v>136644435</v>
       </c>
       <c r="B84" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         <v>136644436</v>
       </c>
       <c r="B85" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9676,7 +9676,7 @@
         <v>136644439</v>
       </c>
       <c r="B86" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>

--- a/artfynd/A 17406-2025 artfynd.xlsx
+++ b/artfynd/A 17406-2025 artfynd.xlsx
@@ -3339,7 +3339,7 @@
         <v>136644424</v>
       </c>
       <c r="B27" t="n">
-        <v>96588</v>
+        <v>96601</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -6646,7 +6646,7 @@
         <v>136644437</v>
       </c>
       <c r="B58" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -8980,7 +8980,7 @@
         <v>136644422</v>
       </c>
       <c r="B80" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
         <v>136644430</v>
       </c>
       <c r="B81" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9212,7 +9212,7 @@
         <v>136644431</v>
       </c>
       <c r="B82" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9328,7 +9328,7 @@
         <v>136644434</v>
       </c>
       <c r="B83" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9444,7 +9444,7 @@
         <v>136644435</v>
       </c>
       <c r="B84" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         <v>136644436</v>
       </c>
       <c r="B85" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9676,7 +9676,7 @@
         <v>136644439</v>
       </c>
       <c r="B86" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>

--- a/artfynd/A 17406-2025 artfynd.xlsx
+++ b/artfynd/A 17406-2025 artfynd.xlsx
@@ -3339,7 +3339,7 @@
         <v>136644424</v>
       </c>
       <c r="B27" t="n">
-        <v>96601</v>
+        <v>96603</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -6646,7 +6646,7 @@
         <v>136644437</v>
       </c>
       <c r="B58" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -8980,7 +8980,7 @@
         <v>136644422</v>
       </c>
       <c r="B80" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
         <v>136644430</v>
       </c>
       <c r="B81" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9212,7 +9212,7 @@
         <v>136644431</v>
       </c>
       <c r="B82" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9328,7 +9328,7 @@
         <v>136644434</v>
       </c>
       <c r="B83" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9444,7 +9444,7 @@
         <v>136644435</v>
       </c>
       <c r="B84" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         <v>136644436</v>
       </c>
       <c r="B85" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9676,7 +9676,7 @@
         <v>136644439</v>
       </c>
       <c r="B86" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>

--- a/artfynd/A 17406-2025 artfynd.xlsx
+++ b/artfynd/A 17406-2025 artfynd.xlsx
@@ -3339,7 +3339,7 @@
         <v>136644424</v>
       </c>
       <c r="B27" t="n">
-        <v>96603</v>
+        <v>96606</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -6646,7 +6646,7 @@
         <v>136644437</v>
       </c>
       <c r="B58" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -8980,7 +8980,7 @@
         <v>136644422</v>
       </c>
       <c r="B80" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
         <v>136644430</v>
       </c>
       <c r="B81" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9212,7 +9212,7 @@
         <v>136644431</v>
       </c>
       <c r="B82" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9328,7 +9328,7 @@
         <v>136644434</v>
       </c>
       <c r="B83" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9444,7 +9444,7 @@
         <v>136644435</v>
       </c>
       <c r="B84" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         <v>136644436</v>
       </c>
       <c r="B85" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9676,7 +9676,7 @@
         <v>136644439</v>
       </c>
       <c r="B86" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>

--- a/artfynd/A 17406-2025 artfynd.xlsx
+++ b/artfynd/A 17406-2025 artfynd.xlsx
@@ -3339,7 +3339,7 @@
         <v>136644424</v>
       </c>
       <c r="B27" t="n">
-        <v>96606</v>
+        <v>96616</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -6646,7 +6646,7 @@
         <v>136644437</v>
       </c>
       <c r="B58" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7306,7 +7306,7 @@
         <v>136644428</v>
       </c>
       <c r="B64" t="n">
-        <v>4783</v>
+        <v>4789</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7422,7 +7422,7 @@
         <v>136644432</v>
       </c>
       <c r="B65" t="n">
-        <v>4783</v>
+        <v>4789</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8980,7 +8980,7 @@
         <v>136644422</v>
       </c>
       <c r="B80" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
         <v>136644430</v>
       </c>
       <c r="B81" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9212,7 +9212,7 @@
         <v>136644431</v>
       </c>
       <c r="B82" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9328,7 +9328,7 @@
         <v>136644434</v>
       </c>
       <c r="B83" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9444,7 +9444,7 @@
         <v>136644435</v>
       </c>
       <c r="B84" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         <v>136644436</v>
       </c>
       <c r="B85" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9676,7 +9676,7 @@
         <v>136644439</v>
       </c>
       <c r="B86" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>

--- a/artfynd/A 17406-2025 artfynd.xlsx
+++ b/artfynd/A 17406-2025 artfynd.xlsx
@@ -3339,7 +3339,7 @@
         <v>136644424</v>
       </c>
       <c r="B27" t="n">
-        <v>96616</v>
+        <v>96617</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -6646,7 +6646,7 @@
         <v>136644437</v>
       </c>
       <c r="B58" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -8980,7 +8980,7 @@
         <v>136644422</v>
       </c>
       <c r="B80" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
         <v>136644430</v>
       </c>
       <c r="B81" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9212,7 +9212,7 @@
         <v>136644431</v>
       </c>
       <c r="B82" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9328,7 +9328,7 @@
         <v>136644434</v>
       </c>
       <c r="B83" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9444,7 +9444,7 @@
         <v>136644435</v>
       </c>
       <c r="B84" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         <v>136644436</v>
       </c>
       <c r="B85" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9676,7 +9676,7 @@
         <v>136644439</v>
       </c>
       <c r="B86" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>

--- a/artfynd/A 17406-2025 artfynd.xlsx
+++ b/artfynd/A 17406-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ93"/>
+  <dimension ref="A1:AZ122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3559,10 +3559,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128760316</v>
+        <v>137385203</v>
       </c>
       <c r="B29" t="n">
-        <v>91680</v>
+        <v>96747</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3570,21 +3570,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3215</v>
+        <v>2818</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3594,13 +3594,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>699935</v>
+        <v>699953</v>
       </c>
       <c r="R29" t="n">
-        <v>6660294</v>
+        <v>6660366</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3624,12 +3624,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3644,49 +3654,49 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Gillis Aronsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128760316</t>
+          <t>https://artportalen.se/Sighting/137385203</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128760310</v>
+        <v>128760316</v>
       </c>
       <c r="B30" t="n">
-        <v>91361</v>
+        <v>91680</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3286</v>
+        <v>3215</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3696,10 +3706,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>699951</v>
+        <v>699935</v>
       </c>
       <c r="R30" t="n">
-        <v>6660295</v>
+        <v>6660294</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3757,53 +3767,54 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128760310</t>
+          <t>https://artportalen.se/Sighting/128760316</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>112662551</v>
+        <v>128760310</v>
       </c>
       <c r="B31" t="n">
-        <v>87412</v>
+        <v>91361</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3624</v>
+        <v>3286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
+          <t>Clavariadelphus truncatus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Quél.) Donk</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>699830</v>
+        <v>699951</v>
       </c>
       <c r="R31" t="n">
-        <v>6660298</v>
+        <v>6660295</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3827,12 +3838,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3841,38 +3852,33 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Birgitta Wasstorp, Eva Grönlund</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112662551</t>
+          <t>https://artportalen.se/Sighting/128760310</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>82416825</v>
+        <v>112662551</v>
       </c>
       <c r="B32" t="n">
-        <v>87309</v>
+        <v>87412</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3880,40 +3886,36 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3674</v>
+        <v>3624</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lundås, Hallstavik, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>699838</v>
+        <v>699830</v>
       </c>
       <c r="R32" t="n">
-        <v>6660371</v>
+        <v>6660298</v>
       </c>
       <c r="S32" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3937,12 +3939,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2019-10-09</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2019-10-09</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3963,7 +3965,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Ossian Rydebjörk, Birgitta Wasstorp, Eva Grönlund</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -3973,13 +3975,13 @@
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82416825</t>
+          <t>https://artportalen.se/Sighting/112662551</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>112662525</v>
+        <v>82416825</v>
       </c>
       <c r="B33" t="n">
         <v>87309</v>
@@ -4013,17 +4015,17 @@
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Lundås, Hallstavik, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>699802</v>
+        <v>699838</v>
       </c>
       <c r="R33" t="n">
-        <v>6660244</v>
+        <v>6660371</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4047,12 +4049,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2019-10-09</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2019-10-09</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4073,7 +4075,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Birgitta Wasstorp, Eva Grönlund</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4083,13 +4085,13 @@
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112662525</t>
+          <t>https://artportalen.se/Sighting/82416825</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>112662546</v>
+        <v>112662525</v>
       </c>
       <c r="B34" t="n">
         <v>87309</v>
@@ -4127,10 +4129,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>699830</v>
+        <v>699802</v>
       </c>
       <c r="R34" t="n">
-        <v>6660298</v>
+        <v>6660244</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4193,13 +4195,13 @@
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112662546</t>
+          <t>https://artportalen.se/Sighting/112662525</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>112662602</v>
+        <v>112662546</v>
       </c>
       <c r="B35" t="n">
         <v>87309</v>
@@ -4237,13 +4239,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>699809</v>
+        <v>699830</v>
       </c>
       <c r="R35" t="n">
-        <v>6660356</v>
+        <v>6660298</v>
       </c>
       <c r="S35" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4303,54 +4305,57 @@
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112662602</t>
+          <t>https://artportalen.se/Sighting/112662546</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128760336</v>
+        <v>112662602</v>
       </c>
       <c r="B36" t="n">
-        <v>87375</v>
+        <v>87309</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3739</v>
+        <v>3674</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>699835</v>
+        <v>699809</v>
       </c>
       <c r="R36" t="n">
-        <v>6660288</v>
+        <v>6660356</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4374,12 +4379,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4388,33 +4393,38 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Gillis Aronsson</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr"/>
+          <t>Ossian Rydebjörk, Birgitta Wasstorp, Eva Grönlund</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128760336</t>
+          <t>https://artportalen.se/Sighting/112662602</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>82416827</v>
+        <v>137385234</v>
       </c>
       <c r="B37" t="n">
-        <v>87146</v>
+        <v>87536</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4422,40 +4432,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3762</v>
+        <v>3674</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lundås, Hallstavik, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>699838</v>
+        <v>699802</v>
       </c>
       <c r="R37" t="n">
-        <v>6660371</v>
+        <v>6660380</v>
       </c>
       <c r="S37" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4479,12 +4486,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2019-10-09</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2019-10-09</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4493,79 +4510,71 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82416827</t>
+          <t>https://artportalen.se/Sighting/137385234</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>112662498</v>
+        <v>128760336</v>
       </c>
       <c r="B38" t="n">
-        <v>87146</v>
+        <v>87375</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>3762</v>
+        <v>3739</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>699752</v>
+        <v>699835</v>
       </c>
       <c r="R38" t="n">
-        <v>6660342</v>
+        <v>6660288</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4589,12 +4598,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4603,35 +4612,30 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Birgitta Wasstorp, Eva Grönlund</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112662498</t>
+          <t>https://artportalen.se/Sighting/128760336</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128760311</v>
+        <v>82416827</v>
       </c>
       <c r="B39" t="n">
         <v>87146</v>
@@ -4660,19 +4664,22 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Lundås, Hallstavik, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>699951</v>
+        <v>699838</v>
       </c>
       <c r="R39" t="n">
-        <v>6660298</v>
+        <v>6660371</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4696,12 +4703,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2019-10-09</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2019-10-09</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4710,30 +4717,35 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Gillis Aronsson</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr"/>
+          <t>Ossian Rydebjörk</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128760311</t>
+          <t>https://artportalen.se/Sighting/82416827</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130379973</v>
+        <v>112662498</v>
       </c>
       <c r="B40" t="n">
         <v>87146</v>
@@ -4762,19 +4774,22 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Svedjan, SSV om Hallstavik, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>699820</v>
+        <v>699752</v>
       </c>
       <c r="R40" t="n">
-        <v>6660145</v>
+        <v>6660342</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4798,12 +4813,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4812,38 +4827,38 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>Äldre, grandominerad barrskog.</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Gillis Aronsson, Cajsa Björkén, Viktor Lund</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr"/>
+          <t>Ossian Rydebjörk, Birgitta Wasstorp, Eva Grönlund</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130379973</t>
+          <t>https://artportalen.se/Sighting/112662498</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124474451</v>
+        <v>128760311</v>
       </c>
       <c r="B41" t="n">
-        <v>91330</v>
+        <v>87146</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4851,37 +4866,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4189</v>
+        <v>3762</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Pers., nom.sanct</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>699943</v>
+        <v>699951</v>
       </c>
       <c r="R41" t="n">
-        <v>6660307</v>
+        <v>6660298</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4908,12 +4920,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4922,79 +4934,71 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124474451</t>
+          <t>https://artportalen.se/Sighting/128760311</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>82416822</v>
+        <v>130379973</v>
       </c>
       <c r="B42" t="n">
-        <v>93189</v>
+        <v>87146</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4361</v>
+        <v>3762</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lundås, Hallstavik, Upl</t>
+          <t>Svedjan, SSV om Hallstavik, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>699838</v>
+        <v>699820</v>
       </c>
       <c r="R42" t="n">
-        <v>6660371</v>
+        <v>6660145</v>
       </c>
       <c r="S42" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5018,12 +5022,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2019-10-09</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2019-10-09</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5032,79 +5036,76 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Äldre, grandominerad barrskog.</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+          <t>Gillis Aronsson, Cajsa Björkén, Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82416822</t>
+          <t>https://artportalen.se/Sighting/130379973</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>112662501</v>
+        <v>137385221</v>
       </c>
       <c r="B43" t="n">
-        <v>93189</v>
+        <v>87373</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4361</v>
+        <v>3762</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>699752</v>
+        <v>699807</v>
       </c>
       <c r="R43" t="n">
-        <v>6660342</v>
+        <v>6660254</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5128,12 +5129,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5142,60 +5153,55 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Birgitta Wasstorp, Eva Grönlund</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112662501</t>
+          <t>https://artportalen.se/Sighting/137385221</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>112662567</v>
+        <v>124474451</v>
       </c>
       <c r="B44" t="n">
-        <v>93189</v>
+        <v>91330</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4361</v>
+        <v>4189</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Pers., nom.sanct</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5208,13 +5214,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>699809</v>
+        <v>699943</v>
       </c>
       <c r="R44" t="n">
-        <v>6660356</v>
+        <v>6660307</v>
       </c>
       <c r="S44" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5238,12 +5244,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5259,12 +5265,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Birgitta Wasstorp, Eva Grönlund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5274,13 +5280,13 @@
       </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112662567</t>
+          <t>https://artportalen.se/Sighting/124474451</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128760327</v>
+        <v>82416822</v>
       </c>
       <c r="B45" t="n">
         <v>93189</v>
@@ -5309,19 +5315,22 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Lundås, Hallstavik, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>699826</v>
+        <v>699838</v>
       </c>
       <c r="R45" t="n">
-        <v>6660373</v>
+        <v>6660371</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5345,12 +5354,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2019-10-09</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2019-10-09</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5359,55 +5368,60 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Gillis Aronsson</t>
-        </is>
-      </c>
-      <c r="AY45" t="inlineStr"/>
+          <t>Ossian Rydebjörk</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128760327</t>
+          <t>https://artportalen.se/Sighting/82416822</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>112662570</v>
+        <v>112662501</v>
       </c>
       <c r="B46" t="n">
-        <v>93193</v>
+        <v>93189</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4363</v>
+        <v>4361</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5420,13 +5434,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>699809</v>
+        <v>699752</v>
       </c>
       <c r="R46" t="n">
-        <v>6660356</v>
+        <v>6660342</v>
       </c>
       <c r="S46" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5486,16 +5500,16 @@
       </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112662570</t>
+          <t>https://artportalen.se/Sighting/112662501</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>112662568</v>
+        <v>112662567</v>
       </c>
       <c r="B47" t="n">
-        <v>93209</v>
+        <v>93189</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5503,21 +5517,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5596,16 +5610,16 @@
       </c>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112662568</t>
+          <t>https://artportalen.se/Sighting/112662567</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128760313</v>
+        <v>128760327</v>
       </c>
       <c r="B48" t="n">
-        <v>93209</v>
+        <v>93189</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5613,21 +5627,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5637,10 +5651,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>699942</v>
+        <v>699826</v>
       </c>
       <c r="R48" t="n">
-        <v>6660292</v>
+        <v>6660373</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5698,54 +5712,57 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128760313</t>
+          <t>https://artportalen.se/Sighting/128760327</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130379975</v>
+        <v>112662570</v>
       </c>
       <c r="B49" t="n">
-        <v>93209</v>
+        <v>93193</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4366</v>
+        <v>4363</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Svedjan, SSV om Hallstavik, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>699783</v>
+        <v>699809</v>
       </c>
       <c r="R49" t="n">
-        <v>6660083</v>
+        <v>6660356</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5769,12 +5786,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5783,38 +5800,38 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>Äldre, grandominerad barrskog.</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Gillis Aronsson, Cajsa Björkén, Viktor Lund</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr"/>
+          <t>Ossian Rydebjörk, Birgitta Wasstorp, Eva Grönlund</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130379975</t>
+          <t>https://artportalen.se/Sighting/112662570</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>112662497</v>
+        <v>112662568</v>
       </c>
       <c r="B50" t="n">
-        <v>91424</v>
+        <v>93209</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5822,21 +5839,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5733</v>
+        <v>4366</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Såpfingersvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Ramaria lutea</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Vent.) Schild</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5849,13 +5866,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>699752</v>
+        <v>699809</v>
       </c>
       <c r="R50" t="n">
-        <v>6660342</v>
+        <v>6660356</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5891,7 +5908,7 @@
         <v>0</v>
       </c>
       <c r="AE50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
@@ -5915,38 +5932,38 @@
       </c>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112662497</t>
+          <t>https://artportalen.se/Sighting/112662568</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128760322</v>
+        <v>128760313</v>
       </c>
       <c r="B51" t="n">
-        <v>91398</v>
+        <v>93209</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5745</v>
+        <v>4366</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gyllenfingersvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Ramaria brunneicontusa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5956,10 +5973,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>699806</v>
+        <v>699942</v>
       </c>
       <c r="R51" t="n">
-        <v>6660365</v>
+        <v>6660292</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6017,57 +6034,54 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128760322</t>
+          <t>https://artportalen.se/Sighting/128760313</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>112662544</v>
+        <v>130379975</v>
       </c>
       <c r="B52" t="n">
-        <v>91435</v>
+        <v>93209</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5747</v>
+        <v>4366</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Svedjan, SSV om Hallstavik, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>699830</v>
+        <v>699783</v>
       </c>
       <c r="R52" t="n">
-        <v>6660298</v>
+        <v>6660083</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6091,12 +6105,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6105,60 +6119,60 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>Äldre, grandominerad barrskog.</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Birgitta Wasstorp, Eva Grönlund</t>
-        </is>
-      </c>
-      <c r="AY52" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+          <t>Gillis Aronsson, Cajsa Björkén, Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112662544</t>
+          <t>https://artportalen.se/Sighting/130379975</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128760320</v>
+        <v>137385238</v>
       </c>
       <c r="B53" t="n">
-        <v>91435</v>
+        <v>93475</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5747</v>
+        <v>4366</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6168,13 +6182,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>699820</v>
+        <v>699807</v>
       </c>
       <c r="R53" t="n">
-        <v>6660298</v>
+        <v>6660362</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6198,12 +6212,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6218,27 +6242,27 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Gillis Aronsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128760320</t>
+          <t>https://artportalen.se/Sighting/137385238</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128760334</v>
+        <v>137385206</v>
       </c>
       <c r="B54" t="n">
-        <v>92928</v>
+        <v>89374</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6246,21 +6270,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5836</v>
+        <v>4405</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Guldkremla</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Russula aurea</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Pers.</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6270,13 +6294,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>699664</v>
+        <v>699926</v>
       </c>
       <c r="R54" t="n">
-        <v>6660365</v>
+        <v>6660293</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6300,12 +6324,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6320,65 +6354,65 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Gillis Aronsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128760334</t>
+          <t>https://artportalen.se/Sighting/137385206</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124444432</v>
+        <v>137385209</v>
       </c>
       <c r="B55" t="n">
-        <v>93233</v>
+        <v>89374</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5964</v>
+        <v>4405</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>699938</v>
+        <v>699837</v>
       </c>
       <c r="R55" t="n">
-        <v>6660298</v>
+        <v>6660285</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6402,12 +6436,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6422,65 +6466,65 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124444432</t>
+          <t>https://artportalen.se/Sighting/137385209</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124445128</v>
+        <v>137385220</v>
       </c>
       <c r="B56" t="n">
-        <v>93233</v>
+        <v>89374</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5964</v>
+        <v>4405</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>699954</v>
+        <v>699801</v>
       </c>
       <c r="R56" t="n">
-        <v>6660370</v>
+        <v>6660252</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6504,12 +6548,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6524,49 +6578,49 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124445128</t>
+          <t>https://artportalen.se/Sighting/137385220</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128760312</v>
+        <v>137385199</v>
       </c>
       <c r="B57" t="n">
-        <v>93233</v>
+        <v>93134</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6576,13 +6630,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>699945</v>
+        <v>699923</v>
       </c>
       <c r="R57" t="n">
-        <v>6660298</v>
+        <v>6660423</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6606,12 +6660,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6626,49 +6690,49 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Gillis Aronsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128760312</t>
+          <t>https://artportalen.se/Sighting/137385199</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>136644437</v>
+        <v>137385212</v>
       </c>
       <c r="B58" t="n">
-        <v>93492</v>
+        <v>93134</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6678,10 +6742,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>699790</v>
+        <v>699831</v>
       </c>
       <c r="R58" t="n">
-        <v>6660268</v>
+        <v>6660271</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6708,22 +6772,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6746,23 +6810,19 @@
           <t>Tomas Falk</t>
         </is>
       </c>
-      <c r="AY58" t="inlineStr">
-        <is>
-          <t>Upplands kalkbarrskogar</t>
-        </is>
-      </c>
+      <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136644437</t>
+          <t>https://artportalen.se/Sighting/137385212</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124449907</v>
+        <v>137385216</v>
       </c>
       <c r="B59" t="n">
-        <v>57950</v>
+        <v>93134</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6770,42 +6830,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>4769</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>699754</v>
+        <v>699823</v>
       </c>
       <c r="R59" t="n">
-        <v>6660376</v>
+        <v>6660293</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6829,12 +6884,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6849,27 +6914,27 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124449907</t>
+          <t>https://artportalen.se/Sighting/137385216</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124451081</v>
+        <v>137385217</v>
       </c>
       <c r="B60" t="n">
-        <v>57950</v>
+        <v>93134</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6877,42 +6942,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>4769</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>699683</v>
+        <v>699824</v>
       </c>
       <c r="R60" t="n">
-        <v>6660350</v>
+        <v>6660277</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6936,12 +6996,22 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6956,27 +7026,27 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124451081</t>
+          <t>https://artportalen.se/Sighting/137385217</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130379971</v>
+        <v>137385228</v>
       </c>
       <c r="B61" t="n">
-        <v>57950</v>
+        <v>93134</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6984,46 +7054,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>4769</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Svedjan, SSV om Hallstavik, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>699710</v>
+        <v>699773</v>
       </c>
       <c r="R61" t="n">
-        <v>6660225</v>
+        <v>6660319</v>
       </c>
       <c r="S61" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7047,12 +7108,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7063,36 +7134,31 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AI61" t="inlineStr">
-        <is>
-          <t>Äldre, grandominerad barrskog.</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Gillis Aronsson, Cajsa Björkén</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130379971</t>
+          <t>https://artportalen.se/Sighting/137385228</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124445043</v>
+        <v>137385232</v>
       </c>
       <c r="B62" t="n">
-        <v>5179</v>
+        <v>93134</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7100,42 +7166,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100526</v>
+        <v>4769</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>699954</v>
+        <v>699777</v>
       </c>
       <c r="R62" t="n">
-        <v>6660370</v>
+        <v>6660396</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7159,12 +7220,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7179,70 +7250,68 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124445043</t>
+          <t>https://artportalen.se/Sighting/137385232</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124447074</v>
+        <v>112662497</v>
       </c>
       <c r="B63" t="n">
-        <v>5179</v>
+        <v>91424</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100526</v>
+        <v>5733</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Såpfingersvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Ramaria lutea</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Vent.) Schild</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>699804</v>
+        <v>699752</v>
       </c>
       <c r="R63" t="n">
-        <v>6660392</v>
+        <v>6660342</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7266,69 +7335,74 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr"/>
+          <t>Ossian Rydebjörk, Birgitta Wasstorp, Eva Grönlund</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124447074</t>
+          <t>https://artportalen.se/Sighting/112662497</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>136644428</v>
+        <v>128760322</v>
       </c>
       <c r="B64" t="n">
-        <v>4789</v>
+        <v>91398</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>102306</v>
+        <v>5745</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Gyllenfingersvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Ramaria brunneicontusa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7338,13 +7412,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>699947</v>
+        <v>699806</v>
       </c>
       <c r="R64" t="n">
-        <v>6660329</v>
+        <v>6660365</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7368,22 +7442,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>11:41</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>11:41</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7398,69 +7462,68 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
-        </is>
-      </c>
-      <c r="AY64" t="inlineStr">
-        <is>
-          <t>Upplands kalkbarrskogar</t>
-        </is>
-      </c>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136644428</t>
+          <t>https://artportalen.se/Sighting/128760322</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>136644432</v>
+        <v>112662544</v>
       </c>
       <c r="B65" t="n">
-        <v>4789</v>
+        <v>91435</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>102306</v>
+        <v>5747</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>699856</v>
+        <v>699830</v>
       </c>
       <c r="R65" t="n">
-        <v>6660318</v>
+        <v>6660298</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7484,22 +7547,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>11:49</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>11:49</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7508,77 +7561,73 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Ossian Rydebjörk, Birgitta Wasstorp, Eva Grönlund</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
-          <t>Upplands kalkbarrskogar</t>
+          <t>Svampar i Roslagen</t>
         </is>
       </c>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136644432</t>
+          <t>https://artportalen.se/Sighting/112662544</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124444974</v>
+        <v>128760320</v>
       </c>
       <c r="B66" t="n">
-        <v>5199</v>
+        <v>91435</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>105930</v>
+        <v>5747</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>699954</v>
+        <v>699820</v>
       </c>
       <c r="R66" t="n">
-        <v>6660370</v>
+        <v>6660298</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7605,12 +7654,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7625,27 +7674,27 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124444974</t>
+          <t>https://artportalen.se/Sighting/128760320</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>105298082</v>
+        <v>128760334</v>
       </c>
       <c r="B67" t="n">
-        <v>99096</v>
+        <v>92928</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7653,21 +7702,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>219798</v>
+        <v>5836</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Guldkremla</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Russula aurea</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Pers.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7677,10 +7726,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>699586</v>
+        <v>699664</v>
       </c>
       <c r="R67" t="n">
-        <v>6660420</v>
+        <v>6660365</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7707,12 +7756,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2022-10-10</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2022-10-10</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7727,65 +7776,65 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/105298082</t>
+          <t>https://artportalen.se/Sighting/128760334</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>105298083</v>
+        <v>124444432</v>
       </c>
       <c r="B68" t="n">
-        <v>99096</v>
+        <v>93233</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>219798</v>
+        <v>5964</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>699594</v>
+        <v>699938</v>
       </c>
       <c r="R68" t="n">
-        <v>6660387</v>
+        <v>6660298</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7809,12 +7858,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2022-10-10</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2022-10-10</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7829,62 +7878,62 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Viktor Lund, Martin Axegård</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/105298083</t>
+          <t>https://artportalen.se/Sighting/124444432</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>105298085</v>
+        <v>124445128</v>
       </c>
       <c r="B69" t="n">
-        <v>99096</v>
+        <v>93233</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>219798</v>
+        <v>5964</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>699604</v>
+        <v>699954</v>
       </c>
       <c r="R69" t="n">
-        <v>6660405</v>
+        <v>6660370</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7911,12 +7960,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2022-10-10</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2022-10-10</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7931,71 +7980,62 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Viktor Lund, Martin Axegård</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/105298085</t>
+          <t>https://artportalen.se/Sighting/124445128</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124447516</v>
+        <v>128760312</v>
       </c>
       <c r="B70" t="n">
-        <v>99118</v>
+        <v>93233</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>699800</v>
+        <v>699945</v>
       </c>
       <c r="R70" t="n">
-        <v>6660415</v>
+        <v>6660298</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8022,12 +8062,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8042,65 +8082,65 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124447516</t>
+          <t>https://artportalen.se/Sighting/128760312</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124454215</v>
+        <v>136644437</v>
       </c>
       <c r="B71" t="n">
-        <v>97983</v>
+        <v>93492</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221945</v>
+        <v>5964</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>699929</v>
+        <v>699790</v>
       </c>
       <c r="R71" t="n">
-        <v>6660329</v>
+        <v>6660268</v>
       </c>
       <c r="S71" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8124,12 +8164,22 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8144,49 +8194,53 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY71" t="inlineStr"/>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr">
+        <is>
+          <t>Upplands kalkbarrskogar</t>
+        </is>
+      </c>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124454215</t>
+          <t>https://artportalen.se/Sighting/136644437</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>105298080</v>
+        <v>137385200</v>
       </c>
       <c r="B72" t="n">
-        <v>101326</v>
+        <v>93499</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8196,13 +8250,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>699598</v>
+        <v>699901</v>
       </c>
       <c r="R72" t="n">
-        <v>6660467</v>
+        <v>6660371</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8226,12 +8280,22 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2022-10-10</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2022-10-10</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8246,65 +8310,65 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/105298080</t>
+          <t>https://artportalen.se/Sighting/137385200</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124444956</v>
+        <v>137385201</v>
       </c>
       <c r="B73" t="n">
-        <v>101326</v>
+        <v>93499</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>699944</v>
+        <v>699921</v>
       </c>
       <c r="R73" t="n">
-        <v>6660374</v>
+        <v>6660357</v>
       </c>
       <c r="S73" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8328,12 +8392,22 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8348,65 +8422,65 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124444956</t>
+          <t>https://artportalen.se/Sighting/137385201</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124446528</v>
+        <v>137385204</v>
       </c>
       <c r="B74" t="n">
-        <v>101326</v>
+        <v>93499</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>699808</v>
+        <v>699938</v>
       </c>
       <c r="R74" t="n">
-        <v>6660347</v>
+        <v>6660319</v>
       </c>
       <c r="S74" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8430,12 +8504,22 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8450,65 +8534,65 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124446528</t>
+          <t>https://artportalen.se/Sighting/137385204</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124450248</v>
+        <v>137385207</v>
       </c>
       <c r="B75" t="n">
-        <v>101326</v>
+        <v>93499</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>699796</v>
+        <v>699901</v>
       </c>
       <c r="R75" t="n">
-        <v>6660315</v>
+        <v>6660296</v>
       </c>
       <c r="S75" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8532,12 +8616,22 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8552,65 +8646,65 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124450248</t>
+          <t>https://artportalen.se/Sighting/137385207</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124451595</v>
+        <v>137385213</v>
       </c>
       <c r="B76" t="n">
-        <v>101326</v>
+        <v>93499</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>699683</v>
+        <v>699832</v>
       </c>
       <c r="R76" t="n">
-        <v>6660350</v>
+        <v>6660319</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8634,12 +8728,22 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8654,65 +8758,65 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124451595</t>
+          <t>https://artportalen.se/Sighting/137385213</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124452710</v>
+        <v>137385219</v>
       </c>
       <c r="B77" t="n">
-        <v>101326</v>
+        <v>93499</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>699855</v>
+        <v>699789</v>
       </c>
       <c r="R77" t="n">
-        <v>6660145</v>
+        <v>6660267</v>
       </c>
       <c r="S77" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8736,12 +8840,22 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8756,49 +8870,49 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124452710</t>
+          <t>https://artportalen.se/Sighting/137385219</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124474452</v>
+        <v>137385229</v>
       </c>
       <c r="B78" t="n">
-        <v>101326</v>
+        <v>93499</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8808,13 +8922,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>699807</v>
+        <v>699668</v>
       </c>
       <c r="R78" t="n">
-        <v>6660377</v>
+        <v>6660395</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8838,12 +8952,22 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8858,49 +8982,49 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124474452</t>
+          <t>https://artportalen.se/Sighting/137385229</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124474453</v>
+        <v>137385235</v>
       </c>
       <c r="B79" t="n">
-        <v>101326</v>
+        <v>93499</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8910,13 +9034,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>699934</v>
+        <v>699800</v>
       </c>
       <c r="R79" t="n">
-        <v>6660275</v>
+        <v>6660368</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8940,12 +9064,22 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8960,49 +9094,49 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124474453</t>
+          <t>https://artportalen.se/Sighting/137385235</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>136644422</v>
+        <v>137385241</v>
       </c>
       <c r="B80" t="n">
-        <v>101620</v>
+        <v>93499</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9012,10 +9146,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>699910</v>
+        <v>699834</v>
       </c>
       <c r="R80" t="n">
-        <v>6660374</v>
+        <v>6660356</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9042,22 +9176,22 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9080,45 +9214,41 @@
           <t>Tomas Falk</t>
         </is>
       </c>
-      <c r="AY80" t="inlineStr">
-        <is>
-          <t>Upplands kalkbarrskogar</t>
-        </is>
-      </c>
+      <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136644422</t>
+          <t>https://artportalen.se/Sighting/137385241</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>136644430</v>
+        <v>137385242</v>
       </c>
       <c r="B81" t="n">
-        <v>101620</v>
+        <v>93499</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9128,10 +9258,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>699943</v>
+        <v>699844</v>
       </c>
       <c r="R81" t="n">
-        <v>6660327</v>
+        <v>6660358</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9158,22 +9288,22 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9196,23 +9326,19 @@
           <t>Tomas Falk</t>
         </is>
       </c>
-      <c r="AY81" t="inlineStr">
-        <is>
-          <t>Upplands kalkbarrskogar</t>
-        </is>
-      </c>
+      <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136644430</t>
+          <t>https://artportalen.se/Sighting/137385242</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>136644431</v>
+        <v>124449907</v>
       </c>
       <c r="B82" t="n">
-        <v>101620</v>
+        <v>57950</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9220,37 +9346,42 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>699947</v>
+        <v>699754</v>
       </c>
       <c r="R82" t="n">
-        <v>6660312</v>
+        <v>6660376</v>
       </c>
       <c r="S82" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9274,22 +9405,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>11:44</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>11:44</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9304,31 +9425,27 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
-        </is>
-      </c>
-      <c r="AY82" t="inlineStr">
-        <is>
-          <t>Upplands kalkbarrskogar</t>
-        </is>
-      </c>
+          <t>Viktor Lund, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136644431</t>
+          <t>https://artportalen.se/Sighting/124449907</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>136644434</v>
+        <v>124451081</v>
       </c>
       <c r="B83" t="n">
-        <v>101620</v>
+        <v>57950</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9336,37 +9453,42 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>699842</v>
+        <v>699683</v>
       </c>
       <c r="R83" t="n">
-        <v>6660319</v>
+        <v>6660350</v>
       </c>
       <c r="S83" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9390,22 +9512,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>12:07</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>12:07</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9420,31 +9532,27 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
-        </is>
-      </c>
-      <c r="AY83" t="inlineStr">
-        <is>
-          <t>Upplands kalkbarrskogar</t>
-        </is>
-      </c>
+          <t>Viktor Lund, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136644434</t>
+          <t>https://artportalen.se/Sighting/124451081</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>136644435</v>
+        <v>130379971</v>
       </c>
       <c r="B84" t="n">
-        <v>101620</v>
+        <v>57950</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9452,37 +9560,46 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Svedjan, SSV om Hallstavik, Upl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>699842</v>
+        <v>699710</v>
       </c>
       <c r="R84" t="n">
-        <v>6660285</v>
+        <v>6660225</v>
       </c>
       <c r="S84" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9506,22 +9623,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>12:09</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>12:09</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9532,35 +9639,36 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
+      </c>
+      <c r="AI84" t="inlineStr">
+        <is>
+          <t>Äldre, grandominerad barrskog.</t>
+        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
-        </is>
-      </c>
-      <c r="AY84" t="inlineStr">
-        <is>
-          <t>Upplands kalkbarrskogar</t>
-        </is>
-      </c>
+          <t>Gillis Aronsson, Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136644435</t>
+          <t>https://artportalen.se/Sighting/130379971</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>136644436</v>
+        <v>124445043</v>
       </c>
       <c r="B85" t="n">
-        <v>101620</v>
+        <v>5179</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9568,37 +9676,42 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>699794</v>
+        <v>699954</v>
       </c>
       <c r="R85" t="n">
-        <v>6660269</v>
+        <v>6660370</v>
       </c>
       <c r="S85" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9622,22 +9735,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>12:12</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>12:12</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9652,31 +9755,27 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
-        </is>
-      </c>
-      <c r="AY85" t="inlineStr">
-        <is>
-          <t>Upplands kalkbarrskogar</t>
-        </is>
-      </c>
+          <t>Viktor Lund, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136644436</t>
+          <t>https://artportalen.se/Sighting/124445043</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>136644439</v>
+        <v>124447074</v>
       </c>
       <c r="B86" t="n">
-        <v>101620</v>
+        <v>5179</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9684,37 +9783,42 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>699782</v>
+        <v>699804</v>
       </c>
       <c r="R86" t="n">
-        <v>6660269</v>
+        <v>6660392</v>
       </c>
       <c r="S86" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9738,22 +9842,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>12:15</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>12:15</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9768,53 +9862,49 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
-        </is>
-      </c>
-      <c r="AY86" t="inlineStr">
-        <is>
-          <t>Upplands kalkbarrskogar</t>
-        </is>
-      </c>
+          <t>Viktor Lund, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136644439</t>
+          <t>https://artportalen.se/Sighting/124447074</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>105298081</v>
+        <v>136644428</v>
       </c>
       <c r="B87" t="n">
-        <v>103403</v>
+        <v>4789</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>223246</v>
+        <v>102306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9824,13 +9914,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>699637</v>
+        <v>699947</v>
       </c>
       <c r="R87" t="n">
-        <v>6660447</v>
+        <v>6660329</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9854,17 +9944,22 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2022-10-10</t>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2022-10-10</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>ungt träd</t>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9879,49 +9974,53 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
-        </is>
-      </c>
-      <c r="AY87" t="inlineStr"/>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr">
+        <is>
+          <t>Upplands kalkbarrskogar</t>
+        </is>
+      </c>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/105298081</t>
+          <t>https://artportalen.se/Sighting/136644428</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>105298084</v>
+        <v>136644432</v>
       </c>
       <c r="B88" t="n">
-        <v>103403</v>
+        <v>4789</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>223246</v>
+        <v>102306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9931,13 +10030,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>699592</v>
+        <v>699856</v>
       </c>
       <c r="R88" t="n">
-        <v>6660391</v>
+        <v>6660318</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9961,17 +10060,22 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2022-10-10</t>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2022-10-10</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>flera unga träd</t>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9986,65 +10090,70 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
-        </is>
-      </c>
-      <c r="AY88" t="inlineStr"/>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr">
+        <is>
+          <t>Upplands kalkbarrskogar</t>
+        </is>
+      </c>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/105298084</t>
+          <t>https://artportalen.se/Sighting/136644432</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>105298088</v>
+        <v>137385215</v>
       </c>
       <c r="B89" t="n">
-        <v>103403</v>
+        <v>58195</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>223246</v>
+        <v>103021</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="M89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>699655</v>
+        <v>699821</v>
       </c>
       <c r="R89" t="n">
-        <v>6660307</v>
+        <v>6660299</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10068,17 +10177,22 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2022-10-10</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2022-10-10</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>ungt träd</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10093,62 +10207,67 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/105298088</t>
+          <t>https://artportalen.se/Sighting/137385215</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>105298089</v>
+        <v>124444974</v>
       </c>
       <c r="B90" t="n">
-        <v>103403</v>
+        <v>5199</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>223246</v>
+        <v>105930</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>699671</v>
+        <v>699954</v>
       </c>
       <c r="R90" t="n">
-        <v>6660294</v>
+        <v>6660370</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10175,17 +10294,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2022-10-10</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2022-10-10</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>ett par stycken ganska unga träd</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10200,49 +10314,49 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Viktor Lund, Martin Axegård</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/105298089</t>
+          <t>https://artportalen.se/Sighting/124444974</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>105298090</v>
+        <v>105298082</v>
       </c>
       <c r="B91" t="n">
-        <v>103403</v>
+        <v>99096</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>223246</v>
+        <v>219798</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10252,10 +10366,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>699721</v>
+        <v>699586</v>
       </c>
       <c r="R91" t="n">
-        <v>6660259</v>
+        <v>6660420</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10290,11 +10404,6 @@
           <t>2022-10-10</t>
         </is>
       </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>ungt träd</t>
-        </is>
-      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
@@ -10318,57 +10427,54 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/105298090</t>
+          <t>https://artportalen.se/Sighting/105298082</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>112662524</v>
+        <v>105298083</v>
       </c>
       <c r="B92" t="n">
-        <v>92688</v>
+        <v>99096</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>232138</v>
+        <v>219798</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Gul lammticka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Albatrellus citrinus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Ryman</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>699802</v>
+        <v>699594</v>
       </c>
       <c r="R92" t="n">
-        <v>6660244</v>
+        <v>6660387</v>
       </c>
       <c r="S92" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10392,12 +10498,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2022-10-10</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2022-10-10</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10406,60 +10512,55 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Niina Sallmén</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Birgitta Wasstorp, Eva Grönlund</t>
-        </is>
-      </c>
-      <c r="AY92" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112662524</t>
+          <t>https://artportalen.se/Sighting/105298083</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128760332</v>
+        <v>105298085</v>
       </c>
       <c r="B93" t="n">
-        <v>92688</v>
+        <v>99096</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>232138</v>
+        <v>219798</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Gul lammticka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Albatrellus citrinus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Ryman</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10469,10 +10570,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>699706</v>
+        <v>699604</v>
       </c>
       <c r="R93" t="n">
-        <v>6660389</v>
+        <v>6660405</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10499,12 +10600,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2022-10-10</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2022-10-10</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10519,18 +10620,3167 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Niina Sallmén</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Gillis Aronsson</t>
+          <t>Niina Sallmén</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/105298085</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>137385222</v>
+      </c>
+      <c r="B94" t="n">
+        <v>99435</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Lundås, Upl</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>699811</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6660125</v>
+      </c>
+      <c r="S94" t="n">
+        <v>5</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137385222</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>124447516</v>
+      </c>
+      <c r="B95" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Svedjan, Upl</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>699800</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6660415</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124447516</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>124454215</v>
+      </c>
+      <c r="B96" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Svedjan, Upl</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>699929</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6660329</v>
+      </c>
+      <c r="S96" t="n">
+        <v>15</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124454215</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>105298080</v>
+      </c>
+      <c r="B97" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Lundås, Upl</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>699598</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6660467</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2022-10-10</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2022-10-10</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105298080</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>124444956</v>
+      </c>
+      <c r="B98" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Svedjan, Upl</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>699944</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6660374</v>
+      </c>
+      <c r="S98" t="n">
+        <v>15</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124444956</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>124446528</v>
+      </c>
+      <c r="B99" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Svedjan, Upl</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>699808</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6660347</v>
+      </c>
+      <c r="S99" t="n">
+        <v>15</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124446528</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>124450248</v>
+      </c>
+      <c r="B100" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Svedjan, Upl</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>699796</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6660315</v>
+      </c>
+      <c r="S100" t="n">
+        <v>15</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124450248</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>124451595</v>
+      </c>
+      <c r="B101" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Svedjan, Upl</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>699683</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6660350</v>
+      </c>
+      <c r="S101" t="n">
+        <v>10</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124451595</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>124452710</v>
+      </c>
+      <c r="B102" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Svedjan, Upl</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>699855</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6660145</v>
+      </c>
+      <c r="S102" t="n">
+        <v>15</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124452710</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>124474452</v>
+      </c>
+      <c r="B103" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Lundås, Upl</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>699807</v>
+      </c>
+      <c r="R103" t="n">
+        <v>6660377</v>
+      </c>
+      <c r="S103" t="n">
+        <v>10</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124474452</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>124474453</v>
+      </c>
+      <c r="B104" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Lundås, Upl</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>699934</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6660275</v>
+      </c>
+      <c r="S104" t="n">
+        <v>10</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124474453</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>136644422</v>
+      </c>
+      <c r="B105" t="n">
+        <v>101620</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Lundås, Upl</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>699910</v>
+      </c>
+      <c r="R105" t="n">
+        <v>6660374</v>
+      </c>
+      <c r="S105" t="n">
+        <v>5</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr">
+        <is>
+          <t>Upplands kalkbarrskogar</t>
+        </is>
+      </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136644422</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>136644430</v>
+      </c>
+      <c r="B106" t="n">
+        <v>101620</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Lundås, Upl</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>699943</v>
+      </c>
+      <c r="R106" t="n">
+        <v>6660327</v>
+      </c>
+      <c r="S106" t="n">
+        <v>5</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr">
+        <is>
+          <t>Upplands kalkbarrskogar</t>
+        </is>
+      </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136644430</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>136644431</v>
+      </c>
+      <c r="B107" t="n">
+        <v>101620</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Lundås, Upl</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>699947</v>
+      </c>
+      <c r="R107" t="n">
+        <v>6660312</v>
+      </c>
+      <c r="S107" t="n">
+        <v>5</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr">
+        <is>
+          <t>Upplands kalkbarrskogar</t>
+        </is>
+      </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136644431</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>136644434</v>
+      </c>
+      <c r="B108" t="n">
+        <v>101620</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Lundås, Upl</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>699842</v>
+      </c>
+      <c r="R108" t="n">
+        <v>6660319</v>
+      </c>
+      <c r="S108" t="n">
+        <v>5</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr">
+        <is>
+          <t>Upplands kalkbarrskogar</t>
+        </is>
+      </c>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136644434</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>136644435</v>
+      </c>
+      <c r="B109" t="n">
+        <v>101620</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Lundås, Upl</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>699842</v>
+      </c>
+      <c r="R109" t="n">
+        <v>6660285</v>
+      </c>
+      <c r="S109" t="n">
+        <v>5</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr">
+        <is>
+          <t>Upplands kalkbarrskogar</t>
+        </is>
+      </c>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136644435</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>136644436</v>
+      </c>
+      <c r="B110" t="n">
+        <v>101620</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Lundås, Upl</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>699794</v>
+      </c>
+      <c r="R110" t="n">
+        <v>6660269</v>
+      </c>
+      <c r="S110" t="n">
+        <v>5</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr">
+        <is>
+          <t>Upplands kalkbarrskogar</t>
+        </is>
+      </c>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136644436</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>136644439</v>
+      </c>
+      <c r="B111" t="n">
+        <v>101620</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Lundås, Upl</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>699782</v>
+      </c>
+      <c r="R111" t="n">
+        <v>6660269</v>
+      </c>
+      <c r="S111" t="n">
+        <v>5</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr">
+        <is>
+          <t>Upplands kalkbarrskogar</t>
+        </is>
+      </c>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136644439</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>137385224</v>
+      </c>
+      <c r="B112" t="n">
+        <v>101628</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Lundås, Upl</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>699758</v>
+      </c>
+      <c r="R112" t="n">
+        <v>6660097</v>
+      </c>
+      <c r="S112" t="n">
+        <v>5</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137385224</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>137385225</v>
+      </c>
+      <c r="B113" t="n">
+        <v>101628</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Lundås, Upl</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>699764</v>
+      </c>
+      <c r="R113" t="n">
+        <v>6660132</v>
+      </c>
+      <c r="S113" t="n">
+        <v>5</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137385225</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>105298081</v>
+      </c>
+      <c r="B114" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Lundås, Upl</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>699637</v>
+      </c>
+      <c r="R114" t="n">
+        <v>6660447</v>
+      </c>
+      <c r="S114" t="n">
+        <v>10</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2022-10-10</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2022-10-10</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>ungt träd</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105298081</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>105298084</v>
+      </c>
+      <c r="B115" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Lundås, Upl</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>699592</v>
+      </c>
+      <c r="R115" t="n">
+        <v>6660391</v>
+      </c>
+      <c r="S115" t="n">
+        <v>10</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2022-10-10</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2022-10-10</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>flera unga träd</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105298084</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>105298088</v>
+      </c>
+      <c r="B116" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Lundås, Upl</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>699655</v>
+      </c>
+      <c r="R116" t="n">
+        <v>6660307</v>
+      </c>
+      <c r="S116" t="n">
+        <v>10</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2022-10-10</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2022-10-10</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>ungt träd</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105298088</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>105298089</v>
+      </c>
+      <c r="B117" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Lundås, Upl</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>699671</v>
+      </c>
+      <c r="R117" t="n">
+        <v>6660294</v>
+      </c>
+      <c r="S117" t="n">
+        <v>10</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2022-10-10</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2022-10-10</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>ett par stycken ganska unga träd</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105298089</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>105298090</v>
+      </c>
+      <c r="B118" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Lundås, Upl</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>699721</v>
+      </c>
+      <c r="R118" t="n">
+        <v>6660259</v>
+      </c>
+      <c r="S118" t="n">
+        <v>10</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2022-10-10</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2022-10-10</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>ungt träd</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105298090</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>112662524</v>
+      </c>
+      <c r="B119" t="n">
+        <v>92688</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>232138</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Gul lammticka</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Albatrellus citrinus</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Ryman</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Lundås, Upl</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>699802</v>
+      </c>
+      <c r="R119" t="n">
+        <v>6660244</v>
+      </c>
+      <c r="S119" t="n">
+        <v>25</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2023-10-11</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>2023-10-11</t>
+        </is>
+      </c>
+      <c r="AD119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF119" t="inlineStr"/>
+      <c r="AG119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Ossian Rydebjörk</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>Ossian Rydebjörk, Birgitta Wasstorp, Eva Grönlund</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112662524</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>128760332</v>
+      </c>
+      <c r="B120" t="n">
+        <v>92688</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>232138</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Gul lammticka</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Albatrellus citrinus</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Ryman</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Lundås, Upl</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>699706</v>
+      </c>
+      <c r="R120" t="n">
+        <v>6660389</v>
+      </c>
+      <c r="S120" t="n">
+        <v>10</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AD120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/128760332</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>137385211</v>
+      </c>
+      <c r="B121" t="n">
+        <v>92953</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>232138</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Gul lammticka</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Albatrellus citrinus</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Ryman</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Lundås, Upl</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>699836</v>
+      </c>
+      <c r="R121" t="n">
+        <v>6660270</v>
+      </c>
+      <c r="S121" t="n">
+        <v>5</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="AD121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137385211</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>137385237</v>
+      </c>
+      <c r="B122" t="n">
+        <v>87573</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Lundås, Upl</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>699808</v>
+      </c>
+      <c r="R122" t="n">
+        <v>6660365</v>
+      </c>
+      <c r="S122" t="n">
+        <v>5</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AD122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF122" t="inlineStr"/>
+      <c r="AG122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137385237</t>
         </is>
       </c>
     </row>
@@ -10628,6 +13878,35 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 17406-2025 artfynd.xlsx
+++ b/artfynd/A 17406-2025 artfynd.xlsx
@@ -3562,7 +3562,7 @@
         <v>137385203</v>
       </c>
       <c r="B29" t="n">
-        <v>96747</v>
+        <v>96753</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>137385234</v>
       </c>
       <c r="B37" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>137385221</v>
       </c>
       <c r="B43" t="n">
-        <v>87373</v>
+        <v>87378</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6150,7 +6150,7 @@
         <v>137385238</v>
       </c>
       <c r="B53" t="n">
-        <v>93475</v>
+        <v>93481</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6262,7 +6262,7 @@
         <v>137385206</v>
       </c>
       <c r="B54" t="n">
-        <v>89374</v>
+        <v>89379</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6374,7 +6374,7 @@
         <v>137385209</v>
       </c>
       <c r="B55" t="n">
-        <v>89374</v>
+        <v>89379</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6486,7 +6486,7 @@
         <v>137385220</v>
       </c>
       <c r="B56" t="n">
-        <v>89374</v>
+        <v>89379</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6598,7 +6598,7 @@
         <v>137385199</v>
       </c>
       <c r="B57" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6710,7 +6710,7 @@
         <v>137385212</v>
       </c>
       <c r="B58" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         <v>137385216</v>
       </c>
       <c r="B59" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6934,7 +6934,7 @@
         <v>137385217</v>
       </c>
       <c r="B60" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7046,7 +7046,7 @@
         <v>137385228</v>
       </c>
       <c r="B61" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7158,7 +7158,7 @@
         <v>137385232</v>
       </c>
       <c r="B62" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8218,7 +8218,7 @@
         <v>137385200</v>
       </c>
       <c r="B72" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8330,7 +8330,7 @@
         <v>137385201</v>
       </c>
       <c r="B73" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8442,7 +8442,7 @@
         <v>137385204</v>
       </c>
       <c r="B74" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8554,7 +8554,7 @@
         <v>137385207</v>
       </c>
       <c r="B75" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8666,7 +8666,7 @@
         <v>137385213</v>
       </c>
       <c r="B76" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8778,7 +8778,7 @@
         <v>137385219</v>
       </c>
       <c r="B77" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8890,7 +8890,7 @@
         <v>137385229</v>
       </c>
       <c r="B78" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>137385235</v>
       </c>
       <c r="B79" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>137385241</v>
       </c>
       <c r="B80" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
         <v>137385242</v>
       </c>
       <c r="B81" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10114,7 +10114,7 @@
         <v>137385215</v>
       </c>
       <c r="B89" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10640,7 +10640,7 @@
         <v>137385222</v>
       </c>
       <c r="B94" t="n">
-        <v>99435</v>
+        <v>99441</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12593,7 +12593,7 @@
         <v>137385224</v>
       </c>
       <c r="B112" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12705,7 +12705,7 @@
         <v>137385225</v>
       </c>
       <c r="B113" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13564,7 +13564,7 @@
         <v>137385211</v>
       </c>
       <c r="B121" t="n">
-        <v>92953</v>
+        <v>92958</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13676,7 +13676,7 @@
         <v>137385237</v>
       </c>
       <c r="B122" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>

--- a/artfynd/A 17406-2025 artfynd.xlsx
+++ b/artfynd/A 17406-2025 artfynd.xlsx
@@ -3562,7 +3562,7 @@
         <v>137385203</v>
       </c>
       <c r="B29" t="n">
-        <v>96753</v>
+        <v>96765</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>137385234</v>
       </c>
       <c r="B37" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>137385221</v>
       </c>
       <c r="B43" t="n">
-        <v>87378</v>
+        <v>87389</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6150,7 +6150,7 @@
         <v>137385238</v>
       </c>
       <c r="B53" t="n">
-        <v>93481</v>
+        <v>93493</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6262,7 +6262,7 @@
         <v>137385206</v>
       </c>
       <c r="B54" t="n">
-        <v>89379</v>
+        <v>89390</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6374,7 +6374,7 @@
         <v>137385209</v>
       </c>
       <c r="B55" t="n">
-        <v>89379</v>
+        <v>89390</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6486,7 +6486,7 @@
         <v>137385220</v>
       </c>
       <c r="B56" t="n">
-        <v>89379</v>
+        <v>89390</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6598,7 +6598,7 @@
         <v>137385199</v>
       </c>
       <c r="B57" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6710,7 +6710,7 @@
         <v>137385212</v>
       </c>
       <c r="B58" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         <v>137385216</v>
       </c>
       <c r="B59" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6934,7 +6934,7 @@
         <v>137385217</v>
       </c>
       <c r="B60" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7046,7 +7046,7 @@
         <v>137385228</v>
       </c>
       <c r="B61" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7158,7 +7158,7 @@
         <v>137385232</v>
       </c>
       <c r="B62" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8218,7 +8218,7 @@
         <v>137385200</v>
       </c>
       <c r="B72" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8330,7 +8330,7 @@
         <v>137385201</v>
       </c>
       <c r="B73" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8442,7 +8442,7 @@
         <v>137385204</v>
       </c>
       <c r="B74" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8554,7 +8554,7 @@
         <v>137385207</v>
       </c>
       <c r="B75" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8666,7 +8666,7 @@
         <v>137385213</v>
       </c>
       <c r="B76" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8778,7 +8778,7 @@
         <v>137385219</v>
       </c>
       <c r="B77" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8890,7 +8890,7 @@
         <v>137385229</v>
       </c>
       <c r="B78" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>137385235</v>
       </c>
       <c r="B79" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>137385241</v>
       </c>
       <c r="B80" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
         <v>137385242</v>
       </c>
       <c r="B81" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10640,7 +10640,7 @@
         <v>137385222</v>
       </c>
       <c r="B94" t="n">
-        <v>99441</v>
+        <v>99453</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12593,7 +12593,7 @@
         <v>137385224</v>
       </c>
       <c r="B112" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12705,7 +12705,7 @@
         <v>137385225</v>
       </c>
       <c r="B113" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13564,7 +13564,7 @@
         <v>137385211</v>
       </c>
       <c r="B121" t="n">
-        <v>92958</v>
+        <v>92970</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13676,7 +13676,7 @@
         <v>137385237</v>
       </c>
       <c r="B122" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>

--- a/artfynd/A 17406-2025 artfynd.xlsx
+++ b/artfynd/A 17406-2025 artfynd.xlsx
@@ -3562,7 +3562,7 @@
         <v>137385203</v>
       </c>
       <c r="B29" t="n">
-        <v>96765</v>
+        <v>96766</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>137385234</v>
       </c>
       <c r="B37" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>137385221</v>
       </c>
       <c r="B43" t="n">
-        <v>87389</v>
+        <v>87390</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6150,7 +6150,7 @@
         <v>137385238</v>
       </c>
       <c r="B53" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6262,7 +6262,7 @@
         <v>137385206</v>
       </c>
       <c r="B54" t="n">
-        <v>89390</v>
+        <v>89391</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6374,7 +6374,7 @@
         <v>137385209</v>
       </c>
       <c r="B55" t="n">
-        <v>89390</v>
+        <v>89391</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6486,7 +6486,7 @@
         <v>137385220</v>
       </c>
       <c r="B56" t="n">
-        <v>89390</v>
+        <v>89391</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6598,7 +6598,7 @@
         <v>137385199</v>
       </c>
       <c r="B57" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6710,7 +6710,7 @@
         <v>137385212</v>
       </c>
       <c r="B58" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         <v>137385216</v>
       </c>
       <c r="B59" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6934,7 +6934,7 @@
         <v>137385217</v>
       </c>
       <c r="B60" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7046,7 +7046,7 @@
         <v>137385228</v>
       </c>
       <c r="B61" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7158,7 +7158,7 @@
         <v>137385232</v>
       </c>
       <c r="B62" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8218,7 +8218,7 @@
         <v>137385200</v>
       </c>
       <c r="B72" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8330,7 +8330,7 @@
         <v>137385201</v>
       </c>
       <c r="B73" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8442,7 +8442,7 @@
         <v>137385204</v>
       </c>
       <c r="B74" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8554,7 +8554,7 @@
         <v>137385207</v>
       </c>
       <c r="B75" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8666,7 +8666,7 @@
         <v>137385213</v>
       </c>
       <c r="B76" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8778,7 +8778,7 @@
         <v>137385219</v>
       </c>
       <c r="B77" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8890,7 +8890,7 @@
         <v>137385229</v>
       </c>
       <c r="B78" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>137385235</v>
       </c>
       <c r="B79" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>137385241</v>
       </c>
       <c r="B80" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
         <v>137385242</v>
       </c>
       <c r="B81" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10640,7 +10640,7 @@
         <v>137385222</v>
       </c>
       <c r="B94" t="n">
-        <v>99453</v>
+        <v>99454</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12593,7 +12593,7 @@
         <v>137385224</v>
       </c>
       <c r="B112" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12705,7 +12705,7 @@
         <v>137385225</v>
       </c>
       <c r="B113" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13564,7 +13564,7 @@
         <v>137385211</v>
       </c>
       <c r="B121" t="n">
-        <v>92970</v>
+        <v>92971</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13676,7 +13676,7 @@
         <v>137385237</v>
       </c>
       <c r="B122" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>

--- a/artfynd/A 17406-2025 artfynd.xlsx
+++ b/artfynd/A 17406-2025 artfynd.xlsx
@@ -3562,7 +3562,7 @@
         <v>137385203</v>
       </c>
       <c r="B29" t="n">
-        <v>96766</v>
+        <v>96769</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>137385234</v>
       </c>
       <c r="B37" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>137385221</v>
       </c>
       <c r="B43" t="n">
-        <v>87390</v>
+        <v>87393</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6150,7 +6150,7 @@
         <v>137385238</v>
       </c>
       <c r="B53" t="n">
-        <v>93494</v>
+        <v>93497</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6262,7 +6262,7 @@
         <v>137385206</v>
       </c>
       <c r="B54" t="n">
-        <v>89391</v>
+        <v>89394</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6374,7 +6374,7 @@
         <v>137385209</v>
       </c>
       <c r="B55" t="n">
-        <v>89391</v>
+        <v>89394</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6486,7 +6486,7 @@
         <v>137385220</v>
       </c>
       <c r="B56" t="n">
-        <v>89391</v>
+        <v>89394</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6598,7 +6598,7 @@
         <v>137385199</v>
       </c>
       <c r="B57" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6710,7 +6710,7 @@
         <v>137385212</v>
       </c>
       <c r="B58" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         <v>137385216</v>
       </c>
       <c r="B59" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6934,7 +6934,7 @@
         <v>137385217</v>
       </c>
       <c r="B60" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7046,7 +7046,7 @@
         <v>137385228</v>
       </c>
       <c r="B61" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7158,7 +7158,7 @@
         <v>137385232</v>
       </c>
       <c r="B62" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8218,7 +8218,7 @@
         <v>137385200</v>
       </c>
       <c r="B72" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8330,7 +8330,7 @@
         <v>137385201</v>
       </c>
       <c r="B73" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8442,7 +8442,7 @@
         <v>137385204</v>
       </c>
       <c r="B74" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8554,7 +8554,7 @@
         <v>137385207</v>
       </c>
       <c r="B75" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8666,7 +8666,7 @@
         <v>137385213</v>
       </c>
       <c r="B76" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8778,7 +8778,7 @@
         <v>137385219</v>
       </c>
       <c r="B77" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8890,7 +8890,7 @@
         <v>137385229</v>
       </c>
       <c r="B78" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>137385235</v>
       </c>
       <c r="B79" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>137385241</v>
       </c>
       <c r="B80" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
         <v>137385242</v>
       </c>
       <c r="B81" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10640,7 +10640,7 @@
         <v>137385222</v>
       </c>
       <c r="B94" t="n">
-        <v>99454</v>
+        <v>99457</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12593,7 +12593,7 @@
         <v>137385224</v>
       </c>
       <c r="B112" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12705,7 +12705,7 @@
         <v>137385225</v>
       </c>
       <c r="B113" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13564,7 +13564,7 @@
         <v>137385211</v>
       </c>
       <c r="B121" t="n">
-        <v>92971</v>
+        <v>92974</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13676,7 +13676,7 @@
         <v>137385237</v>
       </c>
       <c r="B122" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>

--- a/artfynd/A 17406-2025 artfynd.xlsx
+++ b/artfynd/A 17406-2025 artfynd.xlsx
@@ -3562,7 +3562,7 @@
         <v>137385203</v>
       </c>
       <c r="B29" t="n">
-        <v>96769</v>
+        <v>96773</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>137385234</v>
       </c>
       <c r="B37" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>137385221</v>
       </c>
       <c r="B43" t="n">
-        <v>87393</v>
+        <v>87397</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6150,7 +6150,7 @@
         <v>137385238</v>
       </c>
       <c r="B53" t="n">
-        <v>93497</v>
+        <v>93501</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6262,7 +6262,7 @@
         <v>137385206</v>
       </c>
       <c r="B54" t="n">
-        <v>89394</v>
+        <v>89398</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6374,7 +6374,7 @@
         <v>137385209</v>
       </c>
       <c r="B55" t="n">
-        <v>89394</v>
+        <v>89398</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6486,7 +6486,7 @@
         <v>137385220</v>
       </c>
       <c r="B56" t="n">
-        <v>89394</v>
+        <v>89398</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6598,7 +6598,7 @@
         <v>137385199</v>
       </c>
       <c r="B57" t="n">
-        <v>93156</v>
+        <v>93160</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6710,7 +6710,7 @@
         <v>137385212</v>
       </c>
       <c r="B58" t="n">
-        <v>93156</v>
+        <v>93160</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         <v>137385216</v>
       </c>
       <c r="B59" t="n">
-        <v>93156</v>
+        <v>93160</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6934,7 +6934,7 @@
         <v>137385217</v>
       </c>
       <c r="B60" t="n">
-        <v>93156</v>
+        <v>93160</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7046,7 +7046,7 @@
         <v>137385228</v>
       </c>
       <c r="B61" t="n">
-        <v>93156</v>
+        <v>93160</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7158,7 +7158,7 @@
         <v>137385232</v>
       </c>
       <c r="B62" t="n">
-        <v>93156</v>
+        <v>93160</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8218,7 +8218,7 @@
         <v>137385200</v>
       </c>
       <c r="B72" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8330,7 +8330,7 @@
         <v>137385201</v>
       </c>
       <c r="B73" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8442,7 +8442,7 @@
         <v>137385204</v>
       </c>
       <c r="B74" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8554,7 +8554,7 @@
         <v>137385207</v>
       </c>
       <c r="B75" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8666,7 +8666,7 @@
         <v>137385213</v>
       </c>
       <c r="B76" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8778,7 +8778,7 @@
         <v>137385219</v>
       </c>
       <c r="B77" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8890,7 +8890,7 @@
         <v>137385229</v>
       </c>
       <c r="B78" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>137385235</v>
       </c>
       <c r="B79" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>137385241</v>
       </c>
       <c r="B80" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
         <v>137385242</v>
       </c>
       <c r="B81" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10114,7 +10114,7 @@
         <v>137385215</v>
       </c>
       <c r="B89" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10640,7 +10640,7 @@
         <v>137385222</v>
       </c>
       <c r="B94" t="n">
-        <v>99457</v>
+        <v>99461</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12593,7 +12593,7 @@
         <v>137385224</v>
       </c>
       <c r="B112" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12705,7 +12705,7 @@
         <v>137385225</v>
       </c>
       <c r="B113" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13564,7 +13564,7 @@
         <v>137385211</v>
       </c>
       <c r="B121" t="n">
-        <v>92974</v>
+        <v>92978</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13676,7 +13676,7 @@
         <v>137385237</v>
       </c>
       <c r="B122" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
